--- a/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Surne Bilbao Basket.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Surne Bilbao Basket.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY52"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2174.8</v>
+        <v>2491.92</v>
       </c>
       <c r="C2" t="n">
-        <v>2183.54</v>
+        <v>2497.84</v>
       </c>
       <c r="D2" t="n">
-        <v>108.5851415591196</v>
+        <v>108.5337731800275</v>
       </c>
       <c r="E2" t="n">
-        <v>110.7834067614974</v>
+        <v>110.5755372641963</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5291738879260544</v>
+        <v>0.528169014084507</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1637536752695198</v>
+        <v>0.1608337622233659</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2745490981963928</v>
+        <v>0.2688927943760984</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3113807047949163</v>
+        <v>0.3073440643863179</v>
       </c>
       <c r="J2" t="n">
-        <v>331</v>
+        <v>376</v>
       </c>
       <c r="K2" t="n">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="L2" t="n">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="M2" t="n">
-        <v>372</v>
+        <v>417</v>
       </c>
       <c r="N2" t="n">
-        <v>880</v>
+        <v>1008</v>
       </c>
       <c r="O2" t="n">
-        <v>1243</v>
+        <v>1415</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7180820335066436</v>
+        <v>0.7117706237424547</v>
       </c>
       <c r="Q2" t="n">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="R2" t="n">
-        <v>244</v>
+        <v>276</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1409589832466782</v>
+        <v>0.1388329979879276</v>
       </c>
       <c r="T2" t="n">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="U2" t="n">
-        <v>212</v>
+        <v>247</v>
       </c>
       <c r="V2" t="n">
-        <v>0.122472559214327</v>
+        <v>0.1242454728370221</v>
       </c>
       <c r="W2" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="X2" t="n">
-        <v>149</v>
+        <v>173</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.08607741190063548</v>
+        <v>0.08702213279678069</v>
       </c>
       <c r="Z2" t="n">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="AA2" t="n">
-        <v>603</v>
+        <v>695</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3483535528596187</v>
+        <v>0.3495975855130785</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.7079646017699115</v>
+        <v>0.7123674911660778</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.4139344262295082</v>
+        <v>0.4130434782608696</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.3679245283018868</v>
+        <v>0.3603238866396761</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.4295302013422819</v>
+        <v>0.4046242774566474</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3316749585406302</v>
+        <v>0.3309352517985611</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.415929203539823</v>
+        <v>1.424734982332156</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.7358490566037735</v>
+        <v>0.7206477732793523</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.053191489361702</v>
+        <v>1.036866359447005</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.8487179487179487</v>
+        <v>0.8487584650112867</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.8905109489051095</v>
+        <v>0.8921568627450981</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.72</v>
+        <v>1.753086419753086</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.159600997506234</v>
+        <v>1.197777777777778</v>
       </c>
       <c r="AO2" t="n">
-        <v>4.316708229426434</v>
+        <v>4.417777777777777</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.476309226932669</v>
+        <v>5.615555555555556</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>77.67142857142858</v>
+        <v>77.8725</v>
       </c>
       <c r="C3" t="n">
-        <v>77.98357142857144</v>
+        <v>78.0575</v>
       </c>
       <c r="D3" t="n">
-        <v>108.5851415591196</v>
+        <v>108.5337731800275</v>
       </c>
       <c r="E3" t="n">
-        <v>110.7834067614974</v>
+        <v>110.5755372641963</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5291738879260544</v>
+        <v>0.528169014084507</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1637536752695198</v>
+        <v>0.1608337622233659</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2745490981963928</v>
+        <v>0.2688927943760984</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3113807047949163</v>
+        <v>0.3073440643863179</v>
       </c>
       <c r="J3" t="n">
-        <v>11.82142857142857</v>
+        <v>11.75</v>
       </c>
       <c r="K3" t="n">
-        <v>8.714285714285714</v>
+        <v>8.53125</v>
       </c>
       <c r="L3" t="n">
-        <v>4.607142857142857</v>
+        <v>4.4375</v>
       </c>
       <c r="M3" t="n">
-        <v>13.28571428571429</v>
+        <v>13.03125</v>
       </c>
       <c r="N3" t="n">
-        <v>31.42857142857143</v>
+        <v>31.5</v>
       </c>
       <c r="O3" t="n">
-        <v>44.39285714285715</v>
+        <v>44.21875</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7180820335066437</v>
+        <v>0.7117706237424547</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.607142857142857</v>
+        <v>3.5625</v>
       </c>
       <c r="R3" t="n">
-        <v>8.714285714285714</v>
+        <v>8.625</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1409589832466782</v>
+        <v>0.1388329979879276</v>
       </c>
       <c r="T3" t="n">
-        <v>2.785714285714286</v>
+        <v>2.78125</v>
       </c>
       <c r="U3" t="n">
-        <v>7.571428571428571</v>
+        <v>7.71875</v>
       </c>
       <c r="V3" t="n">
-        <v>0.122472559214327</v>
+        <v>0.1242454728370221</v>
       </c>
       <c r="W3" t="n">
-        <v>2.285714285714286</v>
+        <v>2.1875</v>
       </c>
       <c r="X3" t="n">
-        <v>5.321428571428571</v>
+        <v>5.40625</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.08607741190063548</v>
+        <v>0.08702213279678069</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.142857142857143</v>
+        <v>7.1875</v>
       </c>
       <c r="AA3" t="n">
-        <v>21.53571428571428</v>
+        <v>21.71875</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3483535528596187</v>
+        <v>0.3495975855130785</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.7079646017699114</v>
+        <v>0.7123674911660778</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.4139344262295083</v>
+        <v>0.4130434782608696</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.3679245283018868</v>
+        <v>0.3603238866396761</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.4295302013422819</v>
+        <v>0.4046242774566474</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3316749585406302</v>
+        <v>0.3309352517985611</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.415929203539823</v>
+        <v>1.424734982332156</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.7358490566037735</v>
+        <v>0.7206477732793523</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.053191489361702</v>
+        <v>1.036866359447005</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.8487179487179487</v>
+        <v>0.8487584650112867</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.8905109489051093</v>
+        <v>0.8921568627450981</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.72</v>
+        <v>1.753086419753086</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.159600997506234</v>
+        <v>1.197777777777778</v>
       </c>
       <c r="AO3" t="n">
-        <v>4.316708229426434</v>
+        <v>4.417777777777777</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.476309226932669</v>
+        <v>5.615555555555556</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2192.28</v>
+        <v>2503.76</v>
       </c>
       <c r="C4" t="n">
-        <v>2183.54</v>
+        <v>2497.84</v>
       </c>
       <c r="D4" t="n">
-        <v>110.7834067614974</v>
+        <v>110.5755372641963</v>
       </c>
       <c r="E4" t="n">
-        <v>108.5851415591196</v>
+        <v>108.5337731800275</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5311466372657111</v>
+        <v>0.5316731141199227</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1569871351055437</v>
+        <v>0.1564398112834421</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2931726907630522</v>
+        <v>0.2879719051799824</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2712238147739802</v>
+        <v>0.2722437137330754</v>
       </c>
       <c r="J4" t="n">
-        <v>318</v>
+        <v>365</v>
       </c>
       <c r="K4" t="n">
-        <v>302</v>
+        <v>337</v>
       </c>
       <c r="L4" t="n">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="M4" t="n">
-        <v>357</v>
+        <v>406</v>
       </c>
       <c r="N4" t="n">
-        <v>846</v>
+        <v>971</v>
       </c>
       <c r="O4" t="n">
-        <v>1172</v>
+        <v>1337</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6460859977949284</v>
+        <v>0.6465183752417795</v>
       </c>
       <c r="Q4" t="n">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="R4" t="n">
-        <v>303</v>
+        <v>334</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1670341786108049</v>
+        <v>0.1615087040618955</v>
       </c>
       <c r="T4" t="n">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="U4" t="n">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1240352811466373</v>
+        <v>0.1242746615087041</v>
       </c>
       <c r="W4" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="X4" t="n">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.09095920617420065</v>
+        <v>0.08752417794970986</v>
       </c>
       <c r="Z4" t="n">
-        <v>199</v>
+        <v>233</v>
       </c>
       <c r="AA4" t="n">
-        <v>586</v>
+        <v>688</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3230429988974642</v>
+        <v>0.3326885880077369</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.7218430034129693</v>
+        <v>0.7262528047868362</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.4422442244224423</v>
+        <v>0.4431137724550898</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.3866666666666667</v>
+        <v>0.3813229571984436</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.3535911602209945</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3395904436860068</v>
+        <v>0.3386627906976744</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.443686006825939</v>
+        <v>1.452505609573672</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.7733333333333333</v>
+        <v>0.7626459143968871</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.034620505992011</v>
+        <v>1.025316455696202</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.7930174563591023</v>
+        <v>0.8111111111111111</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.034246575342466</v>
+        <v>1.027439024390244</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.628571428571429</v>
+        <v>1.613445378151261</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.279487179487179</v>
+        <v>1.284424379232506</v>
       </c>
       <c r="AO4" t="n">
-        <v>4.651282051282052</v>
+        <v>4.668171557562077</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.930769230769231</v>
+        <v>5.952595936794582</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>78.2957142857143</v>
+        <v>78.24250000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>77.98357142857144</v>
+        <v>78.0575</v>
       </c>
       <c r="D5" t="n">
-        <v>110.7834067614974</v>
+        <v>110.5755372641963</v>
       </c>
       <c r="E5" t="n">
-        <v>108.5851415591196</v>
+        <v>108.5337731800275</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5311466372657111</v>
+        <v>0.5316731141199227</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1569871351055436</v>
+        <v>0.1564398112834421</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2931726907630522</v>
+        <v>0.2879719051799824</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2712238147739802</v>
+        <v>0.2722437137330754</v>
       </c>
       <c r="J5" t="n">
-        <v>11.35714285714286</v>
+        <v>11.40625</v>
       </c>
       <c r="K5" t="n">
-        <v>10.78571428571429</v>
+        <v>10.53125</v>
       </c>
       <c r="L5" t="n">
-        <v>6.107142857142857</v>
+        <v>6</v>
       </c>
       <c r="M5" t="n">
-        <v>12.75</v>
+        <v>12.6875</v>
       </c>
       <c r="N5" t="n">
-        <v>30.21428571428572</v>
+        <v>30.34375</v>
       </c>
       <c r="O5" t="n">
-        <v>41.85714285714285</v>
+        <v>41.78125</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6460859977949283</v>
+        <v>0.6465183752417795</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.785714285714286</v>
+        <v>4.625</v>
       </c>
       <c r="R5" t="n">
-        <v>10.82142857142857</v>
+        <v>10.4375</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1670341786108048</v>
+        <v>0.1615087040618955</v>
       </c>
       <c r="T5" t="n">
-        <v>3.107142857142857</v>
+        <v>3.0625</v>
       </c>
       <c r="U5" t="n">
-        <v>8.035714285714286</v>
+        <v>8.03125</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1240352811466373</v>
+        <v>0.1242746615087041</v>
       </c>
       <c r="W5" t="n">
-        <v>2.142857142857143</v>
+        <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>5.892857142857143</v>
+        <v>5.65625</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.09095920617420065</v>
+        <v>0.08752417794970986</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.107142857142857</v>
+        <v>7.28125</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.92857142857143</v>
+        <v>21.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3230429988974641</v>
+        <v>0.3326885880077369</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.7218430034129694</v>
+        <v>0.7262528047868362</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.4422442244224423</v>
+        <v>0.4431137724550898</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.3866666666666667</v>
+        <v>0.3813229571984436</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.3535911602209945</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3395904436860068</v>
+        <v>0.3386627906976744</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.443686006825939</v>
+        <v>1.452505609573672</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.7733333333333333</v>
+        <v>0.7626459143968871</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.034620505992011</v>
+        <v>1.025316455696202</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.7930174563591023</v>
+        <v>0.8111111111111111</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.034246575342466</v>
+        <v>1.027439024390244</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.628571428571429</v>
+        <v>1.613445378151261</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.27948717948718</v>
+        <v>1.284424379232506</v>
       </c>
       <c r="AO5" t="n">
-        <v>4.651282051282052</v>
+        <v>4.668171557562077</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.930769230769231</v>
+        <v>5.952595936794582</v>
       </c>
     </row>
     <row r="7">
@@ -1419,40 +1419,40 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C8" t="n">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="D8" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E8" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="F8" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G8" t="n">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="H8" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I8" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="J8" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="K8" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="L8" t="n">
         <v>17</v>
       </c>
       <c r="M8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N8" t="n">
         <v>11</v>
@@ -1461,22 +1461,22 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="Q8" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="R8" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="S8" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="T8" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="U8" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="V8" t="n">
         <v>11</v>
@@ -1488,87 +1488,87 @@
         <v>11</v>
       </c>
       <c r="Y8" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="Z8" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.679</v>
       </c>
       <c r="AB8" t="n">
         <v>19</v>
       </c>
       <c r="AC8" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.5</v>
+        <v>0.487</v>
       </c>
       <c r="AE8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF8" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.409</v>
+        <v>0.357</v>
       </c>
       <c r="AH8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI8" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.167</v>
+        <v>0.176</v>
       </c>
       <c r="AK8" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AL8" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.283</v>
+        <v>0.286</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>578:18</t>
+          <t>645:43</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>270.04</v>
+        <v>296.24</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.456</v>
+        <v>0.446</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.506</v>
+        <v>0.494</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.874</v>
+        <v>0.847</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.137</v>
+        <v>0.142</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.245</v>
+        <v>0.233</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.378</v>
+        <v>1.381</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.216</v>
+        <v>0.212</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.033</v>
+        <v>0.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.097</v>
+        <v>0.095</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.07099999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -1578,64 +1578,64 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>28</v>
+      </c>
+      <c r="C9" t="n">
+        <v>209</v>
+      </c>
+      <c r="D9" t="n">
+        <v>39</v>
+      </c>
+      <c r="E9" t="n">
+        <v>68</v>
+      </c>
+      <c r="F9" t="n">
+        <v>22</v>
+      </c>
+      <c r="G9" t="n">
+        <v>79</v>
+      </c>
+      <c r="H9" t="n">
+        <v>65</v>
+      </c>
+      <c r="I9" t="n">
+        <v>76</v>
+      </c>
+      <c r="J9" t="n">
+        <v>77</v>
+      </c>
+      <c r="K9" t="n">
+        <v>31</v>
+      </c>
+      <c r="L9" t="n">
+        <v>8</v>
+      </c>
+      <c r="M9" t="n">
         <v>24</v>
       </c>
-      <c r="C9" t="n">
-        <v>190</v>
-      </c>
-      <c r="D9" t="n">
-        <v>35</v>
-      </c>
-      <c r="E9" t="n">
-        <v>58</v>
-      </c>
-      <c r="F9" t="n">
-        <v>21</v>
-      </c>
-      <c r="G9" t="n">
-        <v>70</v>
-      </c>
-      <c r="H9" t="n">
-        <v>57</v>
-      </c>
-      <c r="I9" t="n">
-        <v>64</v>
-      </c>
-      <c r="J9" t="n">
-        <v>70</v>
-      </c>
-      <c r="K9" t="n">
-        <v>30</v>
-      </c>
-      <c r="L9" t="n">
-        <v>7</v>
-      </c>
-      <c r="M9" t="n">
-        <v>19</v>
-      </c>
       <c r="N9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Q9" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R9" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="S9" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="T9" t="n">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="U9" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="V9" t="n">
         <v>14</v>
@@ -1647,87 +1647,87 @@
         <v>4</v>
       </c>
       <c r="Y9" t="n">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="Z9" t="n">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.788</v>
       </c>
       <c r="AB9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AC9" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.786</v>
+        <v>0.706</v>
       </c>
       <c r="AE9" t="n">
         <v>10</v>
       </c>
       <c r="AF9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.476</v>
+        <v>0.435</v>
       </c>
       <c r="AH9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.4</v>
+        <v>0.385</v>
       </c>
       <c r="AK9" t="n">
         <v>17</v>
       </c>
       <c r="AL9" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.283</v>
+        <v>0.258</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>439:22</t>
+          <t>506:23</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>186.16</v>
+        <v>211.44</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.52</v>
+        <v>0.49</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.608</v>
+        <v>0.579</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.021</v>
+        <v>0.988</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.161</v>
+        <v>0.147</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.445</v>
+        <v>0.442</v>
       </c>
       <c r="AU9" t="n">
-        <v>2.333</v>
+        <v>2.484</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.196</v>
+        <v>0.193</v>
       </c>
       <c r="AW9" t="n">
         <v>0.018</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.078</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.096</v>
+        <v>0.092</v>
       </c>
     </row>
     <row r="10">
@@ -2214,156 +2214,156 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C13" t="n">
-        <v>352</v>
+        <v>412</v>
       </c>
       <c r="D13" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="E13" t="n">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="F13" t="n">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="G13" t="n">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="H13" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I13" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J13" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="K13" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L13" t="n">
         <v>7</v>
       </c>
       <c r="M13" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="N13" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="Q13" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="R13" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="T13" t="n">
-        <v>212</v>
+        <v>253</v>
       </c>
       <c r="U13" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="V13" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="W13" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="X13" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Y13" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="Z13" t="n">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.771</v>
+        <v>0.781</v>
       </c>
       <c r="AB13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC13" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.31</v>
+        <v>0.303</v>
       </c>
       <c r="AE13" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AF13" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.351</v>
+        <v>0.354</v>
       </c>
       <c r="AH13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AI13" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.375</v>
+        <v>0.378</v>
       </c>
       <c r="AK13" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="AL13" t="n">
-        <v>133</v>
+        <v>158</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.368</v>
+        <v>0.38</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>628:58</t>
+          <t>732:28</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>374.2</v>
+        <v>426.4</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.486</v>
+        <v>0.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.543</v>
+        <v>0.552</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.966</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.134</v>
+        <v>0.124</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.246</v>
+        <v>0.226</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.62</v>
+        <v>0.774</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.276</v>
+        <v>0.269</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.013</v>
+        <v>0.011</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.056</v>
+        <v>0.051</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.046</v>
+        <v>0.053</v>
       </c>
     </row>
     <row r="14">
@@ -2691,156 +2691,156 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>32</v>
+      </c>
+      <c r="C16" t="n">
+        <v>274</v>
+      </c>
+      <c r="D16" t="n">
+        <v>65</v>
+      </c>
+      <c r="E16" t="n">
+        <v>101</v>
+      </c>
+      <c r="F16" t="n">
+        <v>29</v>
+      </c>
+      <c r="G16" t="n">
+        <v>66</v>
+      </c>
+      <c r="H16" t="n">
+        <v>57</v>
+      </c>
+      <c r="I16" t="n">
+        <v>78</v>
+      </c>
+      <c r="J16" t="n">
         <v>28</v>
       </c>
-      <c r="C16" t="n">
-        <v>240</v>
-      </c>
-      <c r="D16" t="n">
-        <v>56</v>
-      </c>
-      <c r="E16" t="n">
-        <v>86</v>
-      </c>
-      <c r="F16" t="n">
+      <c r="K16" t="n">
+        <v>81</v>
+      </c>
+      <c r="L16" t="n">
         <v>27</v>
       </c>
-      <c r="G16" t="n">
-        <v>55</v>
-      </c>
-      <c r="H16" t="n">
-        <v>47</v>
-      </c>
-      <c r="I16" t="n">
-        <v>65</v>
-      </c>
-      <c r="J16" t="n">
-        <v>24</v>
-      </c>
-      <c r="K16" t="n">
-        <v>74</v>
-      </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>23</v>
       </c>
-      <c r="M16" t="n">
-        <v>21</v>
-      </c>
       <c r="N16" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="Q16" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="R16" t="n">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="S16" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="T16" t="n">
-        <v>279</v>
+        <v>309</v>
       </c>
       <c r="U16" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="V16" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="W16" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="X16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y16" t="n">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="Z16" t="n">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.742</v>
+        <v>0.748</v>
       </c>
       <c r="AB16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC16" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.25</v>
+        <v>0.273</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
       </c>
       <c r="AF16" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.273</v>
+        <v>0.231</v>
       </c>
       <c r="AH16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI16" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.462</v>
+        <v>0.412</v>
       </c>
       <c r="AK16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL16" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.5</v>
+        <v>0.449</v>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>533:32</t>
+          <t>593:52</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>195.6</v>
+        <v>231.32</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.708</v>
+        <v>0.681</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.227</v>
+        <v>1.185</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.133</v>
+        <v>0.13</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.333</v>
+        <v>0.341</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.923</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.049</v>
+        <v>0.052</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.158</v>
+        <v>0.155</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.034</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="17">
@@ -2850,40 +2850,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C17" t="n">
-        <v>330</v>
+        <v>379</v>
       </c>
       <c r="D17" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="E17" t="n">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="F17" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="G17" t="n">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="H17" t="n">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="I17" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="J17" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="K17" t="n">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="L17" t="n">
         <v>18</v>
       </c>
       <c r="M17" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="N17" t="n">
         <v>12</v>
@@ -2892,87 +2892,87 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="Q17" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="R17" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="S17" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="T17" t="n">
-        <v>274</v>
+        <v>318</v>
       </c>
       <c r="U17" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="V17" t="n">
         <v>38</v>
       </c>
       <c r="W17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y17" t="n">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="Z17" t="n">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.734</v>
+        <v>0.739</v>
       </c>
       <c r="AB17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AC17" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.386</v>
+        <v>0.375</v>
       </c>
       <c r="AE17" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AF17" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.345</v>
+        <v>0.368</v>
       </c>
       <c r="AH17" t="n">
         <v>8</v>
       </c>
       <c r="AI17" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.4</v>
+        <v>0.364</v>
       </c>
       <c r="AK17" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="AL17" t="n">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.298</v>
+        <v>0.303</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>621:01</t>
+          <t>717:56</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>375.4</v>
+        <v>431</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.475</v>
+        <v>0.471</v>
       </c>
       <c r="AQ17" t="n">
         <v>0.528</v>
@@ -2981,25 +2981,25 @@
         <v>0.879</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.168</v>
+        <v>0.167</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.251</v>
+        <v>0.26</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.048</v>
+        <v>1.111</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.28</v>
+        <v>0.278</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.033</v>
+        <v>0.029</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.114</v>
+        <v>0.116</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.098</v>
+        <v>0.103</v>
       </c>
     </row>
     <row r="18">
@@ -3168,67 +3168,67 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C19" t="n">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="D19" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E19" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F19" t="n">
         <v>2</v>
       </c>
       <c r="G19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H19" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I19" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K19" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="L19" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="M19" t="n">
         <v>10</v>
       </c>
       <c r="N19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="Q19" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R19" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="S19" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="T19" t="n">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="U19" t="n">
         <v>12</v>
       </c>
       <c r="V19" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
@@ -3237,19 +3237,19 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="Z19" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.704</v>
+        <v>0.713</v>
       </c>
       <c r="AB19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC19" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AD19" t="n">
         <v>0.5</v>
@@ -3267,7 +3267,7 @@
         <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
@@ -3283,38 +3283,38 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>335:04</t>
+          <t>375:52</t>
         </is>
       </c>
       <c r="AO19" t="n">
-        <v>107.16</v>
+        <v>117.48</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.606</v>
+        <v>0.597</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.643</v>
+        <v>0.641</v>
       </c>
       <c r="AR19" t="n">
-        <v>0.999</v>
+        <v>0.987</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.224</v>
+        <v>0.23</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.409</v>
+        <v>0.417</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.375</v>
+        <v>0.37</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.148</v>
+        <v>0.145</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.105</v>
+        <v>0.109</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.194</v>
+        <v>0.2</v>
       </c>
       <c r="AY19" t="n">
         <v>0.012</v>
@@ -3327,156 +3327,156 @@
         </is>
       </c>
       <c r="B20" t="n">
+        <v>32</v>
+      </c>
+      <c r="C20" t="n">
+        <v>230</v>
+      </c>
+      <c r="D20" t="n">
+        <v>45</v>
+      </c>
+      <c r="E20" t="n">
+        <v>78</v>
+      </c>
+      <c r="F20" t="n">
+        <v>36</v>
+      </c>
+      <c r="G20" t="n">
+        <v>97</v>
+      </c>
+      <c r="H20" t="n">
+        <v>32</v>
+      </c>
+      <c r="I20" t="n">
+        <v>40</v>
+      </c>
+      <c r="J20" t="n">
         <v>28</v>
       </c>
-      <c r="C20" t="n">
-        <v>197</v>
-      </c>
-      <c r="D20" t="n">
-        <v>35</v>
-      </c>
-      <c r="E20" t="n">
-        <v>65</v>
-      </c>
-      <c r="F20" t="n">
-        <v>33</v>
-      </c>
-      <c r="G20" t="n">
-        <v>83</v>
-      </c>
-      <c r="H20" t="n">
-        <v>28</v>
-      </c>
-      <c r="I20" t="n">
+      <c r="K20" t="n">
+        <v>70</v>
+      </c>
+      <c r="L20" t="n">
+        <v>27</v>
+      </c>
+      <c r="M20" t="n">
+        <v>18</v>
+      </c>
+      <c r="N20" t="n">
+        <v>9</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>29</v>
+      </c>
+      <c r="R20" t="n">
+        <v>63</v>
+      </c>
+      <c r="S20" t="n">
         <v>34</v>
       </c>
-      <c r="J20" t="n">
-        <v>21</v>
-      </c>
-      <c r="K20" t="n">
-        <v>56</v>
-      </c>
-      <c r="L20" t="n">
-        <v>25</v>
-      </c>
-      <c r="M20" t="n">
-        <v>17</v>
-      </c>
-      <c r="N20" t="n">
-        <v>6</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>25</v>
-      </c>
-      <c r="R20" t="n">
-        <v>52</v>
-      </c>
-      <c r="S20" t="n">
-        <v>28</v>
-      </c>
       <c r="T20" t="n">
-        <v>187</v>
+        <v>222</v>
       </c>
       <c r="U20" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="V20" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="W20" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="X20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y20" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="Z20" t="n">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.761</v>
+        <v>0.779</v>
       </c>
       <c r="AB20" t="n">
         <v>4</v>
       </c>
       <c r="AC20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF20" t="n">
         <v>15</v>
       </c>
-      <c r="AD20" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>5</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>13</v>
-      </c>
       <c r="AG20" t="n">
-        <v>0.385</v>
+        <v>0.4</v>
       </c>
       <c r="AH20" t="n">
         <v>16</v>
       </c>
       <c r="AI20" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.516</v>
+        <v>0.471</v>
       </c>
       <c r="AK20" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AL20" t="n">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.327</v>
+        <v>0.317</v>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>592:34</t>
+          <t>676:11</t>
         </is>
       </c>
       <c r="AO20" t="n">
-        <v>187.96</v>
+        <v>221.6</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.571</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.604</v>
+        <v>0.597</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.048</v>
+        <v>1.038</v>
       </c>
       <c r="AS20" t="n">
-        <v>0.133</v>
+        <v>0.131</v>
       </c>
       <c r="AT20" t="n">
-        <v>0.189</v>
+        <v>0.183</v>
       </c>
       <c r="AU20" t="n">
-        <v>0.84</v>
+        <v>0.966</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.147</v>
+        <v>0.152</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.048</v>
+        <v>0.045</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.108</v>
+        <v>0.118</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.029</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="21">
@@ -3486,40 +3486,40 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C21" t="n">
-        <v>285</v>
+        <v>341</v>
       </c>
       <c r="D21" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="E21" t="n">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="F21" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G21" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="H21" t="n">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="I21" t="n">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="J21" t="n">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="K21" t="n">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="L21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M21" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N21" t="n">
         <v>15</v>
@@ -3528,25 +3528,25 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="Q21" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="R21" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="S21" t="n">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="T21" t="n">
-        <v>468</v>
+        <v>550</v>
       </c>
       <c r="U21" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="V21" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="W21" t="n">
         <v>14</v>
@@ -3555,87 +3555,87 @@
         <v>10</v>
       </c>
       <c r="Y21" t="n">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="Z21" t="n">
-        <v>199</v>
+        <v>223</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="AB21" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>38</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>37</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI21" t="n">
         <v>8</v>
       </c>
-      <c r="AC21" t="n">
-        <v>32</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>13</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>34</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0.382</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>5</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>7</v>
-      </c>
       <c r="AJ21" t="n">
-        <v>0.714</v>
+        <v>0.75</v>
       </c>
       <c r="AK21" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AL21" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.452</v>
+        <v>0.455</v>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>667:42</t>
+          <t>769:49</t>
         </is>
       </c>
       <c r="AO21" t="n">
-        <v>288.4</v>
+        <v>334</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.503</v>
+        <v>0.528</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.598</v>
+        <v>0.616</v>
       </c>
       <c r="AR21" t="n">
-        <v>0.988</v>
+        <v>1.021</v>
       </c>
       <c r="AS21" t="n">
-        <v>0.173</v>
+        <v>0.171</v>
       </c>
       <c r="AT21" t="n">
-        <v>0.587</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="AU21" t="n">
-        <v>2.34</v>
+        <v>2.316</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.2</v>
+        <v>0.201</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.034</v>
+        <v>0.031</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.157</v>
+        <v>0.165</v>
       </c>
       <c r="AY21" t="n">
-        <v>0.166</v>
+        <v>0.164</v>
       </c>
     </row>
     <row r="22">
@@ -3645,7 +3645,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C22" t="n">
         <v>29</v>
@@ -3660,7 +3660,7 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22" t="n">
         <v>5</v>
@@ -3672,7 +3672,7 @@
         <v>2</v>
       </c>
       <c r="K22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L22" t="n">
         <v>8</v>
@@ -3687,10 +3687,10 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R22" t="n">
         <v>7</v>
@@ -3699,7 +3699,7 @@
         <v>8</v>
       </c>
       <c r="T22" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="U22" t="n">
         <v>5</v>
@@ -3753,48 +3753,48 @@
         <v>0</v>
       </c>
       <c r="AL22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>108:38</t>
+        </is>
+      </c>
+      <c r="AO22" t="n">
+        <v>28.84</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.006</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="AU22" t="n">
         <v>1</v>
       </c>
-      <c r="AM22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>96:31</t>
-        </is>
-      </c>
-      <c r="AO22" t="n">
-        <v>26.84</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>0.5610000000000001</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>0.037</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>0.238</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>2</v>
-      </c>
       <c r="AV22" t="n">
-        <v>0.129</v>
+        <v>0.123</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.094</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.189</v>
+        <v>0.178</v>
       </c>
       <c r="AY22" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="23">
@@ -3804,22 +3804,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C23" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D23" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E23" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F23" t="n">
         <v>18</v>
       </c>
       <c r="G23" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="H23" t="n">
         <v>1</v>
@@ -3828,13 +3828,13 @@
         <v>2</v>
       </c>
       <c r="J23" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K23" t="n">
         <v>14</v>
       </c>
       <c r="L23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M23" t="n">
         <v>5</v>
@@ -3846,58 +3846,58 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R23" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T23" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="U23" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V23" t="n">
         <v>9</v>
       </c>
       <c r="W23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="X23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z23" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.462</v>
+        <v>0.533</v>
       </c>
       <c r="AB23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.6</v>
+        <v>0.636</v>
       </c>
       <c r="AE23" t="n">
         <v>2</v>
       </c>
       <c r="AF23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AH23" t="n">
         <v>10</v>
@@ -3912,48 +3912,48 @@
         <v>8</v>
       </c>
       <c r="AL23" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.296</v>
+        <v>0.258</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>219:36</t>
+          <t>257:20</t>
         </is>
       </c>
       <c r="AO23" t="n">
-        <v>82.88</v>
+        <v>91.88</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.541</v>
+        <v>0.524</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.541</v>
+        <v>0.525</v>
       </c>
       <c r="AR23" t="n">
-        <v>0.977</v>
+        <v>0.947</v>
       </c>
       <c r="AS23" t="n">
-        <v>0.097</v>
+        <v>0.098</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.014</v>
+        <v>0.012</v>
       </c>
       <c r="AU23" t="n">
-        <v>1</v>
+        <v>1.222</v>
       </c>
       <c r="AV23" t="n">
-        <v>0.175</v>
+        <v>0.165</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.047</v>
+        <v>0.044</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.073</v>
+        <v>0.062</v>
       </c>
       <c r="AY23" t="n">
-        <v>0.011</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="24">
@@ -3963,16 +3963,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C24" t="n">
-        <v>263</v>
+        <v>316</v>
       </c>
       <c r="D24" t="n">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="E24" t="n">
-        <v>141</v>
+        <v>169</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3981,49 +3981,49 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="I24" t="n">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="J24" t="n">
+        <v>55</v>
+      </c>
+      <c r="K24" t="n">
+        <v>140</v>
+      </c>
+      <c r="L24" t="n">
+        <v>70</v>
+      </c>
+      <c r="M24" t="n">
+        <v>17</v>
+      </c>
+      <c r="N24" t="n">
+        <v>55</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
         <v>49</v>
       </c>
-      <c r="K24" t="n">
-        <v>122</v>
-      </c>
-      <c r="L24" t="n">
-        <v>55</v>
-      </c>
-      <c r="M24" t="n">
-        <v>16</v>
-      </c>
-      <c r="N24" t="n">
+      <c r="Q24" t="n">
         <v>49</v>
       </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>43</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>43</v>
-      </c>
       <c r="R24" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="S24" t="n">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="T24" t="n">
-        <v>440</v>
+        <v>527</v>
       </c>
       <c r="U24" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="V24" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="W24" t="n">
         <v>8</v>
@@ -4032,28 +4032,28 @@
         <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="Z24" t="n">
-        <v>237</v>
+        <v>281</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.65</v>
+        <v>0.658</v>
       </c>
       <c r="AB24" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AC24" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.433</v>
+        <v>0.429</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -4078,41 +4078,41 @@
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>646:48</t>
+          <t>747:47</t>
         </is>
       </c>
       <c r="AO24" t="n">
-        <v>240.32</v>
+        <v>284</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.681</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.666</v>
+        <v>0.672</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.094</v>
+        <v>1.113</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.179</v>
+        <v>0.173</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.504</v>
+        <v>0.497</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.14</v>
+        <v>1.122</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.172</v>
+        <v>0.176</v>
       </c>
       <c r="AW24" t="n">
-        <v>0.097</v>
+        <v>0.107</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.215</v>
+        <v>0.213</v>
       </c>
       <c r="AY24" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -4122,61 +4122,61 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C25" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E25" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I25" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J25" t="n">
         <v>17</v>
       </c>
       <c r="K25" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="L25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R25" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="S25" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="T25" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="U25" t="n">
         <v>7</v>
@@ -4191,31 +4191,31 @@
         <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z25" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.545</v>
       </c>
       <c r="AB25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.545</v>
+        <v>0.583</v>
       </c>
       <c r="AE25" t="n">
         <v>4</v>
       </c>
       <c r="AF25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.364</v>
+        <v>0.333</v>
       </c>
       <c r="AH25" t="n">
         <v>1</v>
@@ -4227,51 +4227,51 @@
         <v>0.5</v>
       </c>
       <c r="AK25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.182</v>
+        <v>0.217</v>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>325:56</t>
+          <t>354:48</t>
         </is>
       </c>
       <c r="AO25" t="n">
-        <v>84.84</v>
+        <v>90.72</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.408</v>
+        <v>0.42</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.437</v>
+        <v>0.448</v>
       </c>
       <c r="AR25" t="n">
-        <v>0.719</v>
+        <v>0.739</v>
       </c>
       <c r="AS25" t="n">
-        <v>0.177</v>
+        <v>0.176</v>
       </c>
       <c r="AT25" t="n">
-        <v>0.123</v>
+        <v>0.13</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.133</v>
+        <v>1.062</v>
       </c>
       <c r="AV25" t="n">
-        <v>0.121</v>
+        <v>0.118</v>
       </c>
       <c r="AW25" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.067</v>
       </c>
       <c r="AX25" t="n">
-        <v>0.157</v>
+        <v>0.16</v>
       </c>
       <c r="AY25" t="n">
-        <v>0.022</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="26">
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -4308,10 +4308,10 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="L26" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -4323,7 +4323,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4436,157 +4436,157 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>2711</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>1120</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>868</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>611</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>818</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>539</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>811</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>306</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>223</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>417</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>724</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>737</v>
       </c>
       <c r="T27" t="n">
-        <v>59</v>
+        <v>3038</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>376</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>273</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1415</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>0.712</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>0.413</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>247</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>0.36</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>0.405</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>695</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>0.331</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>6475:00</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>29</v>
+        <v>2797.92</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>0.528</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>0.577</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>0.969</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>0.161</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>0.307</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>1.198</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>0.054</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>0.142</v>
       </c>
       <c r="AY27" t="n">
         <v>0</v>
@@ -4595,157 +4595,157 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Rival</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C28" t="n">
-        <v>2371</v>
+        <v>2762</v>
       </c>
       <c r="D28" t="n">
-        <v>520</v>
+        <v>654</v>
       </c>
       <c r="E28" t="n">
-        <v>979</v>
+        <v>1199</v>
       </c>
       <c r="F28" t="n">
-        <v>264</v>
+        <v>297</v>
       </c>
       <c r="G28" t="n">
-        <v>752</v>
+        <v>869</v>
       </c>
       <c r="H28" t="n">
-        <v>539</v>
+        <v>563</v>
       </c>
       <c r="I28" t="n">
-        <v>720</v>
+        <v>729</v>
       </c>
       <c r="J28" t="n">
-        <v>465</v>
+        <v>569</v>
       </c>
       <c r="K28" t="n">
-        <v>704</v>
+        <v>832</v>
       </c>
       <c r="L28" t="n">
-        <v>274</v>
+        <v>328</v>
       </c>
       <c r="M28" t="n">
-        <v>202</v>
+        <v>239</v>
       </c>
       <c r="N28" t="n">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>401</v>
+        <v>443</v>
       </c>
       <c r="Q28" t="n">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="R28" t="n">
-        <v>634</v>
+        <v>747</v>
       </c>
       <c r="S28" t="n">
-        <v>652</v>
+        <v>715</v>
       </c>
       <c r="T28" t="n">
-        <v>2666</v>
+        <v>3154</v>
       </c>
       <c r="U28" t="n">
-        <v>331</v>
+        <v>365</v>
       </c>
       <c r="V28" t="n">
-        <v>244</v>
+        <v>337</v>
       </c>
       <c r="W28" t="n">
-        <v>129</v>
+        <v>192</v>
       </c>
       <c r="X28" t="n">
-        <v>75</v>
+        <v>119</v>
       </c>
       <c r="Y28" t="n">
-        <v>880</v>
+        <v>971</v>
       </c>
       <c r="Z28" t="n">
-        <v>1243</v>
+        <v>1337</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.708</v>
+        <v>0.726</v>
       </c>
       <c r="AB28" t="n">
-        <v>101</v>
+        <v>148</v>
       </c>
       <c r="AC28" t="n">
-        <v>244</v>
+        <v>334</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.414</v>
+        <v>0.443</v>
       </c>
       <c r="AE28" t="n">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="AF28" t="n">
-        <v>212</v>
+        <v>257</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.368</v>
+        <v>0.381</v>
       </c>
       <c r="AH28" t="n">
         <v>64</v>
       </c>
       <c r="AI28" t="n">
-        <v>149</v>
+        <v>181</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.43</v>
+        <v>0.354</v>
       </c>
       <c r="AK28" t="n">
-        <v>200</v>
+        <v>233</v>
       </c>
       <c r="AL28" t="n">
-        <v>603</v>
+        <v>688</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.332</v>
+        <v>0.339</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>5675:00</t>
+          <t>6475:00</t>
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>2448.8</v>
+        <v>2831.76</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.529</v>
+        <v>0.532</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.579</v>
+        <v>0.578</v>
       </c>
       <c r="AR28" t="n">
-        <v>0.968</v>
+        <v>0.975</v>
       </c>
       <c r="AS28" t="n">
-        <v>0.164</v>
+        <v>0.156</v>
       </c>
       <c r="AT28" t="n">
-        <v>0.311</v>
+        <v>0.272</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.16</v>
+        <v>1.284</v>
       </c>
       <c r="AV28" t="n">
         <v>0.2</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.055</v>
+        <v>0.058</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.141</v>
+        <v>0.146</v>
       </c>
       <c r="AY28" t="n">
         <v>0</v>
@@ -4754,545 +4754,545 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Rival</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>28</v>
-      </c>
-      <c r="C29" t="n">
-        <v>2419</v>
-      </c>
-      <c r="D29" t="n">
-        <v>575</v>
-      </c>
-      <c r="E29" t="n">
-        <v>1063</v>
-      </c>
-      <c r="F29" t="n">
-        <v>259</v>
-      </c>
-      <c r="G29" t="n">
-        <v>751</v>
-      </c>
-      <c r="H29" t="n">
-        <v>492</v>
-      </c>
-      <c r="I29" t="n">
-        <v>637</v>
-      </c>
-      <c r="J29" t="n">
-        <v>499</v>
-      </c>
-      <c r="K29" t="n">
-        <v>724</v>
-      </c>
-      <c r="L29" t="n">
-        <v>292</v>
-      </c>
-      <c r="M29" t="n">
-        <v>213</v>
-      </c>
-      <c r="N29" t="n">
-        <v>163</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>390</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>357</v>
-      </c>
-      <c r="R29" t="n">
-        <v>659</v>
-      </c>
-      <c r="S29" t="n">
-        <v>624</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2760</v>
-      </c>
-      <c r="U29" t="n">
-        <v>318</v>
-      </c>
-      <c r="V29" t="n">
-        <v>302</v>
-      </c>
-      <c r="W29" t="n">
-        <v>171</v>
-      </c>
-      <c r="X29" t="n">
-        <v>105</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>846</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1172</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0.722</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>134</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>303</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0.442</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>87</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>225</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0.387</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>60</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>165</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0.364</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>199</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>586</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>5675:00</t>
-        </is>
-      </c>
-      <c r="AO29" t="n">
-        <v>2484.28</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>0.531</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>0.578</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>0.974</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>0.157</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>0.271</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>1.279</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>0</v>
-      </c>
+          <t>--- PER GAME STATS ---</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr"/>
+      <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr"/>
+      <c r="AL29" t="inlineStr"/>
+      <c r="AM29" t="inlineStr"/>
+      <c r="AN29" t="inlineStr"/>
+      <c r="AO29" t="inlineStr"/>
+      <c r="AP29" t="inlineStr"/>
+      <c r="AQ29" t="inlineStr"/>
+      <c r="AR29" t="inlineStr"/>
+      <c r="AS29" t="inlineStr"/>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AU29" t="inlineStr"/>
+      <c r="AV29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr"/>
+      <c r="AX29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>--- PER GAME STATS ---</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="inlineStr"/>
-      <c r="AB30" t="inlineStr"/>
-      <c r="AC30" t="inlineStr"/>
-      <c r="AD30" t="inlineStr"/>
-      <c r="AE30" t="inlineStr"/>
-      <c r="AF30" t="inlineStr"/>
-      <c r="AG30" t="inlineStr"/>
-      <c r="AH30" t="inlineStr"/>
-      <c r="AI30" t="inlineStr"/>
-      <c r="AJ30" t="inlineStr"/>
-      <c r="AK30" t="inlineStr"/>
-      <c r="AL30" t="inlineStr"/>
-      <c r="AM30" t="inlineStr"/>
-      <c r="AN30" t="inlineStr"/>
-      <c r="AO30" t="inlineStr"/>
-      <c r="AP30" t="inlineStr"/>
-      <c r="AQ30" t="inlineStr"/>
-      <c r="AR30" t="inlineStr"/>
-      <c r="AS30" t="inlineStr"/>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AU30" t="inlineStr"/>
-      <c r="AV30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr"/>
-      <c r="AX30" t="inlineStr"/>
-      <c r="AY30" t="inlineStr"/>
+          <t>#2 M. NORMANTAS (Per Game)</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>32</v>
+      </c>
+      <c r="C30" t="n">
+        <v>7.844</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1.656</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3.375</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.969</v>
+      </c>
+      <c r="G30" t="n">
+        <v>3.594</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2.219</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.812</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1.688</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.312</v>
+      </c>
+      <c r="T30" t="n">
+        <v>237</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.219</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.487</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>3.062</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="AN30" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="AO30" t="n">
+        <v>9.257</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0.446</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0.494</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0.847</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>1.381</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0.212</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0.07099999999999999</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>#2 M. NORMANTAS (Per Game)</t>
+          <t>#3 H. FREY (Per Game)</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>28</v>
       </c>
       <c r="C31" t="n">
-        <v>8.429</v>
+        <v>7.464</v>
       </c>
       <c r="D31" t="n">
-        <v>1.821</v>
+        <v>1.393</v>
       </c>
       <c r="E31" t="n">
-        <v>3.571</v>
+        <v>2.429</v>
       </c>
       <c r="F31" t="n">
+        <v>0.786</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2.821</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2.321</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2.714</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1.107</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.107</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.107</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2.429</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T31" t="n">
+        <v>236</v>
+      </c>
+      <c r="U31" t="n">
         <v>1</v>
       </c>
-      <c r="G31" t="n">
+      <c r="V31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>2.929</v>
+      </c>
+      <c r="Z31" t="n">
         <v>3.714</v>
       </c>
-      <c r="H31" t="n">
-        <v>1.786</v>
-      </c>
-      <c r="I31" t="n">
+      <c r="AA31" t="n">
+        <v>0.788</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.706</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0.821</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0.179</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0.464</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="AL31" t="n">
         <v>2.357</v>
       </c>
-      <c r="J31" t="n">
-        <v>1.821</v>
-      </c>
-      <c r="K31" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0.607</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0.964</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0.393</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1.321</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>1.321</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.786</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T31" t="n">
-        <v>233</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.179</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0.393</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0.643</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0.393</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>2.607</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>3.786</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0.6889999999999999</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0.679</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.357</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>0.321</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>0.786</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0.409</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>0.929</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>3.286</v>
-      </c>
       <c r="AM31" t="n">
-        <v>0.283</v>
+        <v>0.258</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>9.644</v>
+        <v>7.551</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.456</v>
+        <v>0.49</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.506</v>
+        <v>0.579</v>
       </c>
       <c r="AR31" t="n">
-        <v>0.874</v>
+        <v>0.988</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.137</v>
+        <v>0.147</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.245</v>
+        <v>0.442</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.378</v>
+        <v>2.484</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.216</v>
+        <v>0.193</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.033</v>
+        <v>0.018</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.097</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.106</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>#3 H. FREY (Per Game)</t>
+          <t>#4 K. DE CASTRO (Per Game)</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="C32" t="n">
-        <v>7.917</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>1.458</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>2.417</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0.875</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>2.917</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>2.375</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>2.667</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>2.917</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0.292</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.792</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>0.208</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.458</v>
+        <v>0.4</v>
       </c>
       <c r="S32" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>219</v>
+        <v>-2</v>
       </c>
       <c r="U32" t="n">
-        <v>1.042</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>0.583</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.958</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.625</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.8159999999999999</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.458</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.583</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.786</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.417</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.875</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.476</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.417</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>0.708</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.283</v>
+        <v>0</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>00:19</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>7.757</v>
+        <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.608</v>
+        <v>0</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.021</v>
+        <v>0</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.161</v>
+        <v>0</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.445</v>
+        <v>0</v>
       </c>
       <c r="AU32" t="n">
-        <v>2.333</v>
+        <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>0.196</v>
+        <v>0</v>
       </c>
       <c r="AW32" t="n">
-        <v>0.018</v>
+        <v>0</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.078</v>
+        <v>0</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.114</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>#4 K. DE CASTRO (Per Game)</t>
+          <t>#5 B. ERRASTI (Per Game)</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
@@ -5340,13 +5340,13 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -5407,7 +5407,7 @@
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>00:19</t>
+          <t>00:16</t>
         </is>
       </c>
       <c r="AO33" t="n">
@@ -5447,11 +5447,11 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>#5 B. ERRASTI (Per Game)</t>
+          <t>#6 A. MINTEGUI (Per Game)</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -5566,7 +5566,7 @@
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>00:16</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO34" t="n">
@@ -5606,329 +5606,329 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>#6 A. MINTEGUI (Per Game)</t>
+          <t>#7 J. JAWORSKI (Per Game)</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>12.875</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>1.781</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>4.406</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>2.312</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>6.094</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>2.375</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>2.656</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1.281</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>1.031</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>0.219</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>0.656</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>0.594</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.656</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>1.656</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.094</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1.688</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.719</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.438</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>0.719</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>3.125</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>0.781</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>0.312</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.031</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>0.303</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>0.719</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>2.031</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>0.354</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>0.438</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>1.156</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>0.378</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1.875</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>4.938</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>22:53</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>0</v>
+        <v>13.325</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>0.552</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>0.966</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>0.124</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>0.226</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>0.774</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>0.269</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>0.051</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>0.053</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>#7 J. JAWORSKI (Per Game)</t>
+          <t>#8 A. VELASCO (Per Game)</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>12.571</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>4.429</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>2.179</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>5.893</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>2.536</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>2.857</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>1.107</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>1.107</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.643</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>0.607</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>1.786</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.786</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>1.786</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>212</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.786</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.036</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.429</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>4.214</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.771</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.321</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.036</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.714</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.036</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.351</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.429</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.143</v>
+        <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.368</v>
+        <v>0</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>22:27</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>13.364</v>
+        <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.486</v>
+        <v>0</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.543</v>
+        <v>0</v>
       </c>
       <c r="AR36" t="n">
-        <v>0.9409999999999999</v>
+        <v>0</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.134</v>
+        <v>0</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.246</v>
+        <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="AV36" t="n">
-        <v>0.276</v>
+        <v>0</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.056</v>
+        <v>0</v>
       </c>
       <c r="AY36" t="n">
-        <v>0.046</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>#8 A. VELASCO (Per Game)</t>
+          <t>#9 U. MADARIAGA (Per Game)</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
@@ -6083,548 +6083,548 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>#9 U. MADARIAGA (Per Game)</t>
+          <t>#10 M. KRAMPELJ (Per Game)</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>8.561999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>2.031</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>3.156</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>0.906</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>2.062</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>1.781</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>2.438</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>0.875</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>2.531</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>0.844</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>0.719</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>0.875</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>3.375</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>309</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.125</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>0.469</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>3.625</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>4.844</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>0.748</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>0.094</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>0.344</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>0.273</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>0.094</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>0.406</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>0.231</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>0.219</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>0.531</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>0.412</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>1.531</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>0.449</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AO38" t="n">
-        <v>0</v>
+        <v>7.229</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>0.681</v>
       </c>
       <c r="AR38" t="n">
-        <v>0</v>
+        <v>1.185</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>0.341</v>
       </c>
       <c r="AU38" t="n">
-        <v>0</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>0.052</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>0.155</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>0.035</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>#10 M. KRAMPELJ (Per Game)</t>
+          <t>#11 D. HILLIARD (Per Game)</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C39" t="n">
-        <v>8.571</v>
+        <v>12.633</v>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="E39" t="n">
-        <v>3.071</v>
+        <v>5.033</v>
       </c>
       <c r="F39" t="n">
-        <v>0.964</v>
+        <v>1.7</v>
       </c>
       <c r="G39" t="n">
-        <v>1.964</v>
+        <v>5.467</v>
       </c>
       <c r="H39" t="n">
-        <v>1.679</v>
+        <v>2.733</v>
       </c>
       <c r="I39" t="n">
-        <v>2.321</v>
+        <v>3.333</v>
       </c>
       <c r="J39" t="n">
-        <v>0.857</v>
+        <v>2.667</v>
       </c>
       <c r="K39" t="n">
-        <v>2.643</v>
+        <v>2.433</v>
       </c>
       <c r="L39" t="n">
-        <v>0.821</v>
+        <v>0.6</v>
       </c>
       <c r="M39" t="n">
-        <v>0.75</v>
+        <v>0.967</v>
       </c>
       <c r="N39" t="n">
-        <v>0.821</v>
+        <v>0.4</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>0.929</v>
+        <v>2.4</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.929</v>
+        <v>2.4</v>
       </c>
       <c r="R39" t="n">
-        <v>3.321</v>
+        <v>2.233</v>
       </c>
       <c r="S39" t="n">
-        <v>2.464</v>
+        <v>2.533</v>
       </c>
       <c r="T39" t="n">
-        <v>279</v>
+        <v>318</v>
       </c>
       <c r="U39" t="n">
-        <v>1.607</v>
+        <v>1.633</v>
       </c>
       <c r="V39" t="n">
-        <v>0.964</v>
+        <v>1.267</v>
       </c>
       <c r="W39" t="n">
-        <v>0.464</v>
+        <v>0.6</v>
       </c>
       <c r="X39" t="n">
-        <v>0.25</v>
+        <v>0.267</v>
       </c>
       <c r="Y39" t="n">
-        <v>3.5</v>
+        <v>4.067</v>
       </c>
       <c r="Z39" t="n">
-        <v>4.714</v>
+        <v>5.5</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.742</v>
+        <v>0.739</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="AC39" t="n">
-        <v>0.286</v>
+        <v>1.6</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.25</v>
+        <v>0.375</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.107</v>
+        <v>0.467</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.393</v>
+        <v>1.267</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.273</v>
+        <v>0.368</v>
       </c>
       <c r="AH39" t="n">
-        <v>0.214</v>
+        <v>0.267</v>
       </c>
       <c r="AI39" t="n">
-        <v>0.464</v>
+        <v>0.733</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.462</v>
+        <v>0.364</v>
       </c>
       <c r="AK39" t="n">
-        <v>0.75</v>
+        <v>1.433</v>
       </c>
       <c r="AL39" t="n">
-        <v>1.5</v>
+        <v>4.733</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.5</v>
+        <v>0.303</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>23:55</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>6.986</v>
+        <v>14.367</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.471</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.708</v>
+        <v>0.528</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.227</v>
+        <v>0.879</v>
       </c>
       <c r="AS39" t="n">
-        <v>0.133</v>
+        <v>0.167</v>
       </c>
       <c r="AT39" t="n">
-        <v>0.333</v>
+        <v>0.26</v>
       </c>
       <c r="AU39" t="n">
-        <v>0.923</v>
+        <v>1.111</v>
       </c>
       <c r="AV39" t="n">
-        <v>0.17</v>
+        <v>0.278</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.049</v>
+        <v>0.029</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.158</v>
+        <v>0.116</v>
       </c>
       <c r="AY39" t="n">
-        <v>0.034</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>#11 D. HILLIARD (Per Game)</t>
+          <t>#12 A. ZECEVIC (Per Game)</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="C40" t="n">
-        <v>12.692</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>2.423</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>5.038</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>1.731</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>5.538</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>2.654</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>3.269</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>2.538</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>2.385</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0.6919999999999999</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>0.462</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2.423</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.423</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2.346</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>2.577</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>274</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>1.577</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.462</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>0.654</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>0.269</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>4.038</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.734</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.654</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.692</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.386</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.385</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.115</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.345</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>0.308</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.769</v>
+        <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.423</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
-        <v>4.769</v>
+        <v>0</v>
       </c>
       <c r="AM40" t="n">
-        <v>0.298</v>
+        <v>0</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>23:53</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>14.438</v>
+        <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.475</v>
+        <v>0</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.528</v>
+        <v>0</v>
       </c>
       <c r="AR40" t="n">
-        <v>0.879</v>
+        <v>0</v>
       </c>
       <c r="AS40" t="n">
-        <v>0.168</v>
+        <v>0</v>
       </c>
       <c r="AT40" t="n">
-        <v>0.251</v>
+        <v>0</v>
       </c>
       <c r="AU40" t="n">
-        <v>1.048</v>
+        <v>0</v>
       </c>
       <c r="AV40" t="n">
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.033</v>
+        <v>0</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.114</v>
+        <v>0</v>
       </c>
       <c r="AY40" t="n">
-        <v>0.106</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>#12 A. ZECEVIC (Per Game)</t>
+          <t>#13 B. BAGAYOKO (Per Game)</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>3.867</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>1.333</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>0.067</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>0.433</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.933</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>1.533</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="W41" t="n">
         <v>0</v>
@@ -6633,1356 +6633,1356 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>2.067</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>0.713</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>0.067</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AH41" t="n">
         <v>0</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>0.033</v>
       </c>
       <c r="AJ41" t="n">
         <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>0.067</v>
       </c>
       <c r="AL41" t="n">
-        <v>0</v>
+        <v>0.267</v>
       </c>
       <c r="AM41" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AO41" t="n">
-        <v>0</v>
+        <v>3.916</v>
       </c>
       <c r="AP41" t="n">
-        <v>0</v>
+        <v>0.597</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0</v>
+        <v>0.641</v>
       </c>
       <c r="AR41" t="n">
-        <v>0</v>
+        <v>0.987</v>
       </c>
       <c r="AS41" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>0.417</v>
       </c>
       <c r="AU41" t="n">
-        <v>0</v>
+        <v>0.37</v>
       </c>
       <c r="AV41" t="n">
-        <v>0</v>
+        <v>0.145</v>
       </c>
       <c r="AW41" t="n">
-        <v>0</v>
+        <v>0.109</v>
       </c>
       <c r="AX41" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AY41" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>#13 B. BAGAYOKO (Per Game)</t>
+          <t>#18 L. PETRASEK (Per Game)</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C42" t="n">
-        <v>4.115</v>
+        <v>7.188</v>
       </c>
       <c r="D42" t="n">
-        <v>1.423</v>
+        <v>1.406</v>
       </c>
       <c r="E42" t="n">
-        <v>2.231</v>
+        <v>2.438</v>
       </c>
       <c r="F42" t="n">
-        <v>0.077</v>
+        <v>1.125</v>
       </c>
       <c r="G42" t="n">
-        <v>0.308</v>
+        <v>3.031</v>
       </c>
       <c r="H42" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.188</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.969</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="T42" t="n">
+        <v>222</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.344</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>2.094</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>2.688</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0.779</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>1.969</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="AN42" t="inlineStr">
+        <is>
+          <t>21:07</t>
+        </is>
+      </c>
+      <c r="AO42" t="n">
+        <v>6.925</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>0.5659999999999999</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="AR42" t="n">
         <v>1.038</v>
       </c>
-      <c r="I42" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0.346</v>
-      </c>
-      <c r="K42" t="n">
-        <v>2.192</v>
-      </c>
-      <c r="L42" t="n">
-        <v>1.192</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0.462</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0.923</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0.923</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.923</v>
-      </c>
-      <c r="S42" t="n">
-        <v>1.654</v>
-      </c>
-      <c r="T42" t="n">
-        <v>156</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0.462</v>
-      </c>
-      <c r="V42" t="n">
-        <v>0.577</v>
-      </c>
-      <c r="W42" t="n">
-        <v>0</v>
-      </c>
-      <c r="X42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>2.192</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>3.115</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>0.704</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>0.192</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>0.231</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>0.308</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
-      <c r="AO42" t="n">
-        <v>4.122</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>0.606</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>0.643</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>0.999</v>
-      </c>
       <c r="AS42" t="n">
-        <v>0.224</v>
+        <v>0.131</v>
       </c>
       <c r="AT42" t="n">
-        <v>0.409</v>
+        <v>0.183</v>
       </c>
       <c r="AU42" t="n">
-        <v>0.375</v>
+        <v>0.966</v>
       </c>
       <c r="AV42" t="n">
-        <v>0.148</v>
+        <v>0.152</v>
       </c>
       <c r="AW42" t="n">
-        <v>0.105</v>
+        <v>0.045</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.194</v>
+        <v>0.118</v>
       </c>
       <c r="AY42" t="n">
-        <v>0.013</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>#18 L. PETRASEK (Per Game)</t>
+          <t>#19 M. PANTZAR (Per Game)</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C43" t="n">
-        <v>7.036</v>
+        <v>10.656</v>
       </c>
       <c r="D43" t="n">
-        <v>1.25</v>
+        <v>2.031</v>
       </c>
       <c r="E43" t="n">
-        <v>2.321</v>
+        <v>4.625</v>
       </c>
       <c r="F43" t="n">
-        <v>1.179</v>
+        <v>0.969</v>
       </c>
       <c r="G43" t="n">
-        <v>2.964</v>
+        <v>1.969</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>3.688</v>
       </c>
       <c r="I43" t="n">
-        <v>1.214</v>
+        <v>4.688</v>
       </c>
       <c r="J43" t="n">
+        <v>4.125</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>1.781</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1.781</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.469</v>
+      </c>
+      <c r="S43" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T43" t="n">
+        <v>550</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>4.875</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>6.969</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.188</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>1.156</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AJ43" t="n">
         <v>0.75</v>
       </c>
-      <c r="K43" t="n">
-        <v>2</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0.893</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0.607</v>
-      </c>
-      <c r="N43" t="n">
-        <v>0.214</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0.893</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0.893</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.857</v>
-      </c>
-      <c r="S43" t="n">
-        <v>1</v>
-      </c>
-      <c r="T43" t="n">
-        <v>187</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1.286</v>
-      </c>
-      <c r="V43" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="W43" t="n">
-        <v>0.357</v>
-      </c>
-      <c r="X43" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.929</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>2.536</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>0.761</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>0.536</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>0.179</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>0.464</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>1.107</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>0.516</v>
-      </c>
       <c r="AK43" t="n">
-        <v>0.607</v>
+        <v>0.781</v>
       </c>
       <c r="AL43" t="n">
-        <v>1.857</v>
+        <v>1.719</v>
       </c>
       <c r="AM43" t="n">
-        <v>0.327</v>
+        <v>0.455</v>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>21:09</t>
+          <t>24:03</t>
         </is>
       </c>
       <c r="AO43" t="n">
-        <v>6.713</v>
+        <v>10.438</v>
       </c>
       <c r="AP43" t="n">
-        <v>0.571</v>
+        <v>0.528</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.604</v>
+        <v>0.616</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.048</v>
+        <v>1.021</v>
       </c>
       <c r="AS43" t="n">
-        <v>0.133</v>
+        <v>0.171</v>
       </c>
       <c r="AT43" t="n">
-        <v>0.189</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="AU43" t="n">
-        <v>0.84</v>
+        <v>2.316</v>
       </c>
       <c r="AV43" t="n">
-        <v>0.147</v>
+        <v>0.201</v>
       </c>
       <c r="AW43" t="n">
-        <v>0.048</v>
+        <v>0.031</v>
       </c>
       <c r="AX43" t="n">
-        <v>0.108</v>
+        <v>0.165</v>
       </c>
       <c r="AY43" t="n">
-        <v>0.029</v>
+        <v>0.164</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>#19 M. PANTZAR (Per Game)</t>
+          <t>#20 A. SYLLA (Per Game)</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C44" t="n">
-        <v>10.179</v>
+        <v>1.526</v>
       </c>
       <c r="D44" t="n">
-        <v>1.929</v>
+        <v>0.632</v>
       </c>
       <c r="E44" t="n">
-        <v>4.643</v>
+        <v>1.053</v>
       </c>
       <c r="F44" t="n">
-        <v>0.857</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>1.75</v>
+        <v>0.105</v>
       </c>
       <c r="H44" t="n">
-        <v>3.75</v>
+        <v>0.263</v>
       </c>
       <c r="I44" t="n">
-        <v>4.821</v>
+        <v>0.579</v>
       </c>
       <c r="J44" t="n">
-        <v>4.179</v>
+        <v>0.105</v>
       </c>
       <c r="K44" t="n">
-        <v>3.286</v>
+        <v>0.895</v>
       </c>
       <c r="L44" t="n">
-        <v>0.714</v>
+        <v>0.421</v>
       </c>
       <c r="M44" t="n">
-        <v>1.214</v>
+        <v>0.105</v>
       </c>
       <c r="N44" t="n">
-        <v>0.536</v>
+        <v>0.158</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>1.786</v>
+        <v>0.105</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.786</v>
+        <v>0.105</v>
       </c>
       <c r="R44" t="n">
-        <v>1.536</v>
+        <v>0.368</v>
       </c>
       <c r="S44" t="n">
-        <v>4.607</v>
+        <v>0.421</v>
       </c>
       <c r="T44" t="n">
-        <v>468</v>
+        <v>44</v>
       </c>
       <c r="U44" t="n">
-        <v>1.714</v>
+        <v>0.263</v>
       </c>
       <c r="V44" t="n">
-        <v>0.536</v>
+        <v>0.737</v>
       </c>
       <c r="W44" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0.357</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>4.929</v>
+        <v>0.842</v>
       </c>
       <c r="Z44" t="n">
-        <v>7.107</v>
+        <v>1.368</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.615</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.286</v>
+        <v>0.053</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.143</v>
+        <v>0.158</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="AE44" t="n">
-        <v>0.464</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.214</v>
+        <v>0.105</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.382</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>0.179</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0.714</v>
+        <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>0.679</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
-        <v>1.5</v>
+        <v>0.105</v>
       </c>
       <c r="AM44" t="n">
-        <v>0.452</v>
+        <v>0</v>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>23:50</t>
+          <t>05:43</t>
         </is>
       </c>
       <c r="AO44" t="n">
-        <v>10.3</v>
+        <v>1.518</v>
       </c>
       <c r="AP44" t="n">
-        <v>0.503</v>
+        <v>0.545</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.598</v>
+        <v>0.54</v>
       </c>
       <c r="AR44" t="n">
-        <v>0.988</v>
+        <v>1.006</v>
       </c>
       <c r="AS44" t="n">
-        <v>0.173</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AT44" t="n">
-        <v>0.587</v>
+        <v>0.227</v>
       </c>
       <c r="AU44" t="n">
-        <v>2.34</v>
+        <v>1</v>
       </c>
       <c r="AV44" t="n">
-        <v>0.2</v>
+        <v>0.123</v>
       </c>
       <c r="AW44" t="n">
-        <v>0.034</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AX44" t="n">
-        <v>0.157</v>
+        <v>0.178</v>
       </c>
       <c r="AY44" t="n">
-        <v>0.166</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>#20 A. SYLLA (Per Game)</t>
+          <t>#22 A. FONT (Per Game)</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C45" t="n">
-        <v>1.933</v>
+        <v>2.719</v>
       </c>
       <c r="D45" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="E45" t="n">
-        <v>1.333</v>
+        <v>0.906</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="G45" t="n">
-        <v>0.067</v>
+        <v>1.656</v>
       </c>
       <c r="H45" t="n">
-        <v>0.333</v>
+        <v>0.031</v>
       </c>
       <c r="I45" t="n">
-        <v>0.733</v>
+        <v>0.062</v>
       </c>
       <c r="J45" t="n">
-        <v>0.133</v>
+        <v>0.344</v>
       </c>
       <c r="K45" t="n">
-        <v>1.067</v>
+        <v>0.438</v>
       </c>
       <c r="L45" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.344</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="T45" t="n">
+        <v>38</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="AA45" t="n">
         <v>0.533</v>
       </c>
-      <c r="M45" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="S45" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="T45" t="n">
-        <v>45</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="V45" t="n">
-        <v>0.9330000000000001</v>
-      </c>
-      <c r="W45" t="n">
-        <v>0</v>
-      </c>
-      <c r="X45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.067</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>1.733</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>0.615</v>
-      </c>
       <c r="AB45" t="n">
-        <v>0.067</v>
+        <v>0.219</v>
       </c>
       <c r="AC45" t="n">
-        <v>0.2</v>
+        <v>0.344</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.333</v>
+        <v>0.636</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.133</v>
+        <v>0.156</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>0.312</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>0.455</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AL45" t="n">
-        <v>0.067</v>
+        <v>0.969</v>
       </c>
       <c r="AM45" t="n">
-        <v>0</v>
+        <v>0.258</v>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="AO45" t="n">
-        <v>1.789</v>
+        <v>2.871</v>
       </c>
       <c r="AP45" t="n">
-        <v>0.571</v>
+        <v>0.524</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.525</v>
       </c>
       <c r="AR45" t="n">
-        <v>1.08</v>
+        <v>0.947</v>
       </c>
       <c r="AS45" t="n">
-        <v>0.037</v>
+        <v>0.098</v>
       </c>
       <c r="AT45" t="n">
-        <v>0.238</v>
+        <v>0.012</v>
       </c>
       <c r="AU45" t="n">
-        <v>2</v>
+        <v>1.222</v>
       </c>
       <c r="AV45" t="n">
-        <v>0.129</v>
+        <v>0.165</v>
       </c>
       <c r="AW45" t="n">
-        <v>0.094</v>
+        <v>0.044</v>
       </c>
       <c r="AX45" t="n">
-        <v>0.189</v>
+        <v>0.062</v>
       </c>
       <c r="AY45" t="n">
-        <v>0.005</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>#22 A. FONT (Per Game)</t>
+          <t>#32 T. HLINASON (Per Game)</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C46" t="n">
-        <v>2.893</v>
+        <v>9.875</v>
       </c>
       <c r="D46" t="n">
-        <v>0.464</v>
+        <v>3.625</v>
       </c>
       <c r="E46" t="n">
-        <v>0.893</v>
+        <v>5.281</v>
       </c>
       <c r="F46" t="n">
-        <v>0.643</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.036</v>
+        <v>2.625</v>
       </c>
       <c r="I46" t="n">
-        <v>0.07099999999999999</v>
+        <v>4.688</v>
       </c>
       <c r="J46" t="n">
-        <v>0.286</v>
+        <v>1.719</v>
       </c>
       <c r="K46" t="n">
-        <v>0.5</v>
+        <v>4.375</v>
       </c>
       <c r="L46" t="n">
-        <v>0.321</v>
+        <v>2.188</v>
       </c>
       <c r="M46" t="n">
-        <v>0.179</v>
+        <v>0.531</v>
       </c>
       <c r="N46" t="n">
-        <v>0.214</v>
+        <v>1.719</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>0.286</v>
+        <v>1.531</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.286</v>
+        <v>1.531</v>
       </c>
       <c r="R46" t="n">
-        <v>1.321</v>
+        <v>2.438</v>
       </c>
       <c r="S46" t="n">
-        <v>0.179</v>
+        <v>3.75</v>
       </c>
       <c r="T46" t="n">
-        <v>39</v>
+        <v>527</v>
       </c>
       <c r="U46" t="n">
-        <v>0.607</v>
+        <v>0.625</v>
       </c>
       <c r="V46" t="n">
-        <v>0.321</v>
+        <v>1.812</v>
       </c>
       <c r="W46" t="n">
-        <v>0.143</v>
+        <v>0.25</v>
       </c>
       <c r="X46" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.156</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.214</v>
+        <v>5.781</v>
       </c>
       <c r="Z46" t="n">
-        <v>0.464</v>
+        <v>8.781000000000001</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.462</v>
+        <v>0.658</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.214</v>
+        <v>0.469</v>
       </c>
       <c r="AC46" t="n">
-        <v>0.357</v>
+        <v>1.094</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.6</v>
+        <v>0.429</v>
       </c>
       <c r="AE46" t="n">
-        <v>0.07099999999999999</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.143</v>
+        <v>0.094</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>0.357</v>
+        <v>0</v>
       </c>
       <c r="AI46" t="n">
-        <v>0.786</v>
+        <v>0</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0.455</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>0.286</v>
+        <v>0</v>
       </c>
       <c r="AL46" t="n">
-        <v>0.964</v>
+        <v>0</v>
       </c>
       <c r="AM46" t="n">
-        <v>0.296</v>
+        <v>0</v>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AO46" t="n">
-        <v>2.96</v>
+        <v>8.875</v>
       </c>
       <c r="AP46" t="n">
-        <v>0.541</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.541</v>
+        <v>0.672</v>
       </c>
       <c r="AR46" t="n">
-        <v>0.977</v>
+        <v>1.113</v>
       </c>
       <c r="AS46" t="n">
-        <v>0.097</v>
+        <v>0.173</v>
       </c>
       <c r="AT46" t="n">
-        <v>0.014</v>
+        <v>0.497</v>
       </c>
       <c r="AU46" t="n">
-        <v>1</v>
+        <v>1.122</v>
       </c>
       <c r="AV46" t="n">
-        <v>0.175</v>
+        <v>0.176</v>
       </c>
       <c r="AW46" t="n">
-        <v>0.047</v>
+        <v>0.107</v>
       </c>
       <c r="AX46" t="n">
-        <v>0.073</v>
+        <v>0.213</v>
       </c>
       <c r="AY46" t="n">
-        <v>0.011</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>#32 T. HLINASON (Per Game)</t>
+          <t>#73 S. LAZAREVIC (Per Game)</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C47" t="n">
-        <v>9.393000000000001</v>
+        <v>2.68</v>
       </c>
       <c r="D47" t="n">
-        <v>3.429</v>
+        <v>0.8</v>
       </c>
       <c r="E47" t="n">
-        <v>5.036</v>
+        <v>1.76</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>2.536</v>
+        <v>0.36</v>
       </c>
       <c r="I47" t="n">
-        <v>4.571</v>
+        <v>0.52</v>
       </c>
       <c r="J47" t="n">
-        <v>1.75</v>
+        <v>0.68</v>
       </c>
       <c r="K47" t="n">
-        <v>4.357</v>
+        <v>2</v>
       </c>
       <c r="L47" t="n">
-        <v>1.964</v>
+        <v>0.84</v>
       </c>
       <c r="M47" t="n">
-        <v>0.571</v>
+        <v>0.4</v>
       </c>
       <c r="N47" t="n">
-        <v>1.75</v>
+        <v>0.12</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>1.536</v>
+        <v>0.64</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.536</v>
+        <v>0.64</v>
       </c>
       <c r="R47" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="S47" t="n">
-        <v>3.607</v>
+        <v>0.72</v>
       </c>
       <c r="T47" t="n">
-        <v>440</v>
+        <v>65</v>
       </c>
       <c r="U47" t="n">
-        <v>0.429</v>
+        <v>0.28</v>
       </c>
       <c r="V47" t="n">
-        <v>1.679</v>
+        <v>0.16</v>
       </c>
       <c r="W47" t="n">
-        <v>0.286</v>
+        <v>0.04</v>
       </c>
       <c r="X47" t="n">
-        <v>0.179</v>
+        <v>0.04</v>
       </c>
       <c r="Y47" t="n">
-        <v>5.5</v>
+        <v>0.72</v>
       </c>
       <c r="Z47" t="n">
-        <v>8.464</v>
+        <v>1.32</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.65</v>
+        <v>0.545</v>
       </c>
       <c r="AB47" t="n">
-        <v>0.464</v>
+        <v>0.28</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.071</v>
+        <v>0.48</v>
       </c>
       <c r="AD47" t="n">
-        <v>0.433</v>
+        <v>0.583</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.48</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AL47" t="n">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="AM47" t="n">
-        <v>0</v>
+        <v>0.217</v>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>23:06</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AO47" t="n">
-        <v>8.583</v>
+        <v>3.629</v>
       </c>
       <c r="AP47" t="n">
-        <v>0.681</v>
+        <v>0.42</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.666</v>
+        <v>0.448</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.094</v>
+        <v>0.739</v>
       </c>
       <c r="AS47" t="n">
-        <v>0.179</v>
+        <v>0.176</v>
       </c>
       <c r="AT47" t="n">
-        <v>0.504</v>
+        <v>0.13</v>
       </c>
       <c r="AU47" t="n">
-        <v>1.14</v>
+        <v>1.062</v>
       </c>
       <c r="AV47" t="n">
-        <v>0.172</v>
+        <v>0.118</v>
       </c>
       <c r="AW47" t="n">
-        <v>0.097</v>
+        <v>0.067</v>
       </c>
       <c r="AX47" t="n">
-        <v>0.215</v>
+        <v>0.16</v>
       </c>
       <c r="AY47" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>#73 S. LAZAREVIC (Per Game)</t>
+          <t>Equip (Per Game)</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="C48" t="n">
-        <v>2.905</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>0.905</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>1.952</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>0.238</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>1.143</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.381</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>0.524</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>2.143</v>
+        <v>2.188</v>
       </c>
       <c r="L48" t="n">
-        <v>0.952</v>
+        <v>1.125</v>
       </c>
       <c r="M48" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>0.095</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>0.714</v>
+        <v>1.031</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.714</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>2.476</v>
+        <v>0.062</v>
       </c>
       <c r="S48" t="n">
-        <v>0.762</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>0.048</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>0.048</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.429</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.5669999999999999</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.286</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>0.524</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.545</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>0.524</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.364</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>0.048</v>
+        <v>0</v>
       </c>
       <c r="AI48" t="n">
-        <v>0.095</v>
+        <v>0</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AK48" t="n">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="AL48" t="n">
-        <v>1.048</v>
+        <v>0</v>
       </c>
       <c r="AM48" t="n">
-        <v>0.182</v>
+        <v>0</v>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO48" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>0.408</v>
+        <v>0</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.437</v>
+        <v>0</v>
       </c>
       <c r="AR48" t="n">
-        <v>0.719</v>
+        <v>0</v>
       </c>
       <c r="AS48" t="n">
-        <v>0.177</v>
+        <v>0</v>
       </c>
       <c r="AT48" t="n">
-        <v>0.123</v>
+        <v>0</v>
       </c>
       <c r="AU48" t="n">
-        <v>1.133</v>
+        <v>0</v>
       </c>
       <c r="AV48" t="n">
-        <v>0.121</v>
+        <v>0</v>
       </c>
       <c r="AW48" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="AX48" t="n">
-        <v>0.157</v>
+        <v>0</v>
       </c>
       <c r="AY48" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>TOTAL (Per Game)</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>84.71899999999999</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>18.75</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>9.375</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>27.125</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>19.094</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>25.562</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>16.844</v>
       </c>
       <c r="K49" t="n">
-        <v>2</v>
+        <v>25.344</v>
       </c>
       <c r="L49" t="n">
-        <v>1.214</v>
+        <v>9.561999999999999</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>6.969</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>5.625</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>1.036</v>
+        <v>14.062</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>13.031</v>
       </c>
       <c r="R49" t="n">
-        <v>0.07099999999999999</v>
+        <v>22.625</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>23.031</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>3038</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>11.75</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>8.531000000000001</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>4.438</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>2.531</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>31.5</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>44.219</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>0.712</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>3.562</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>8.625</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>0.413</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>2.781</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>7.719</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>0.36</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>2.188</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>5.406</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>0.405</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>7.188</v>
       </c>
       <c r="AL49" t="n">
-        <v>0</v>
+        <v>21.719</v>
       </c>
       <c r="AM49" t="n">
-        <v>0</v>
+        <v>0.331</v>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>202:20</t>
         </is>
       </c>
       <c r="AO49" t="n">
-        <v>0</v>
+        <v>87.435</v>
       </c>
       <c r="AP49" t="n">
-        <v>0</v>
+        <v>0.528</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0</v>
+        <v>0.577</v>
       </c>
       <c r="AR49" t="n">
-        <v>0</v>
+        <v>0.969</v>
       </c>
       <c r="AS49" t="n">
-        <v>0</v>
+        <v>0.161</v>
       </c>
       <c r="AT49" t="n">
-        <v>0</v>
+        <v>0.307</v>
       </c>
       <c r="AU49" t="n">
-        <v>0</v>
+        <v>1.198</v>
       </c>
       <c r="AV49" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AW49" t="n">
-        <v>0</v>
+        <v>0.054</v>
       </c>
       <c r="AX49" t="n">
-        <v>0</v>
+        <v>0.142</v>
       </c>
       <c r="AY49" t="n">
         <v>0</v>
@@ -7991,477 +7991,159 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>Rival (Per Game)</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>86.312</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>20.438</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>37.469</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>9.281000000000001</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>27.156</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>17.594</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>22.781</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>17.781</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>10.25</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>7.469</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>5.688</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>13.844</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>12.688</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>23.344</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>22.344</v>
       </c>
       <c r="T50" t="n">
-        <v>59</v>
+        <v>3154</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>11.406</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>10.531</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>3.719</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>30.344</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>41.781</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>0.726</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>4.625</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>10.438</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>0.443</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>3.062</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>8.031000000000001</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>0.381</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>5.656</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>0.354</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>7.281</v>
       </c>
       <c r="AL50" t="n">
-        <v>0</v>
+        <v>21.5</v>
       </c>
       <c r="AM50" t="n">
-        <v>0</v>
+        <v>0.339</v>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>202:20</t>
         </is>
       </c>
       <c r="AO50" t="n">
-        <v>1.036</v>
+        <v>88.492</v>
       </c>
       <c r="AP50" t="n">
-        <v>0</v>
+        <v>0.532</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0</v>
+        <v>0.578</v>
       </c>
       <c r="AR50" t="n">
-        <v>0</v>
+        <v>0.975</v>
       </c>
       <c r="AS50" t="n">
-        <v>0</v>
+        <v>0.156</v>
       </c>
       <c r="AT50" t="n">
-        <v>0</v>
+        <v>0.272</v>
       </c>
       <c r="AU50" t="n">
-        <v>0</v>
+        <v>1.284</v>
       </c>
       <c r="AV50" t="n">
-        <v>0</v>
+        <v>0.202</v>
       </c>
       <c r="AW50" t="n">
-        <v>0</v>
+        <v>0.058</v>
       </c>
       <c r="AX50" t="n">
-        <v>0</v>
+        <v>0.146</v>
       </c>
       <c r="AY50" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL (Per Game)</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>28</v>
-      </c>
-      <c r="C51" t="n">
-        <v>84.679</v>
-      </c>
-      <c r="D51" t="n">
-        <v>18.571</v>
-      </c>
-      <c r="E51" t="n">
-        <v>34.964</v>
-      </c>
-      <c r="F51" t="n">
-        <v>9.429</v>
-      </c>
-      <c r="G51" t="n">
-        <v>26.857</v>
-      </c>
-      <c r="H51" t="n">
-        <v>19.25</v>
-      </c>
-      <c r="I51" t="n">
-        <v>25.714</v>
-      </c>
-      <c r="J51" t="n">
-        <v>16.607</v>
-      </c>
-      <c r="K51" t="n">
-        <v>25.143</v>
-      </c>
-      <c r="L51" t="n">
-        <v>9.786</v>
-      </c>
-      <c r="M51" t="n">
-        <v>7.214</v>
-      </c>
-      <c r="N51" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>14.321</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>13.286</v>
-      </c>
-      <c r="R51" t="n">
-        <v>22.643</v>
-      </c>
-      <c r="S51" t="n">
-        <v>23.286</v>
-      </c>
-      <c r="T51" t="n">
-        <v>2666</v>
-      </c>
-      <c r="U51" t="n">
-        <v>11.821</v>
-      </c>
-      <c r="V51" t="n">
-        <v>8.714</v>
-      </c>
-      <c r="W51" t="n">
-        <v>4.607</v>
-      </c>
-      <c r="X51" t="n">
-        <v>2.679</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>31.429</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>44.393</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>0.708</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>3.607</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>8.714</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>0.414</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>2.786</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>7.571</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>0.368</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>2.286</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>5.321</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>7.143</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>21.536</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>0.332</v>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>202:40</t>
-        </is>
-      </c>
-      <c r="AO51" t="n">
-        <v>87.45699999999999</v>
-      </c>
-      <c r="AP51" t="n">
-        <v>0.529</v>
-      </c>
-      <c r="AQ51" t="n">
-        <v>0.579</v>
-      </c>
-      <c r="AR51" t="n">
-        <v>0.968</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>0.164</v>
-      </c>
-      <c r="AT51" t="n">
-        <v>0.311</v>
-      </c>
-      <c r="AU51" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AV51" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="AX51" t="n">
-        <v>0.141</v>
-      </c>
-      <c r="AY51" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="inlineStr">
-        <is>
-          <t>Rival (Per Game)</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>28</v>
-      </c>
-      <c r="C52" t="n">
-        <v>86.393</v>
-      </c>
-      <c r="D52" t="n">
-        <v>20.536</v>
-      </c>
-      <c r="E52" t="n">
-        <v>37.964</v>
-      </c>
-      <c r="F52" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="G52" t="n">
-        <v>26.821</v>
-      </c>
-      <c r="H52" t="n">
-        <v>17.571</v>
-      </c>
-      <c r="I52" t="n">
-        <v>22.75</v>
-      </c>
-      <c r="J52" t="n">
-        <v>17.821</v>
-      </c>
-      <c r="K52" t="n">
-        <v>25.857</v>
-      </c>
-      <c r="L52" t="n">
-        <v>10.429</v>
-      </c>
-      <c r="M52" t="n">
-        <v>7.607</v>
-      </c>
-      <c r="N52" t="n">
-        <v>5.821</v>
-      </c>
-      <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" t="n">
-        <v>13.929</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>12.75</v>
-      </c>
-      <c r="R52" t="n">
-        <v>23.536</v>
-      </c>
-      <c r="S52" t="n">
-        <v>22.286</v>
-      </c>
-      <c r="T52" t="n">
-        <v>2760</v>
-      </c>
-      <c r="U52" t="n">
-        <v>11.357</v>
-      </c>
-      <c r="V52" t="n">
-        <v>10.786</v>
-      </c>
-      <c r="W52" t="n">
-        <v>6.107</v>
-      </c>
-      <c r="X52" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>30.214</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>41.857</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>0.722</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>4.786</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>10.821</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>0.442</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>3.107</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>8.036</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>0.387</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>2.143</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>5.893</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>0.364</v>
-      </c>
-      <c r="AK52" t="n">
-        <v>7.107</v>
-      </c>
-      <c r="AL52" t="n">
-        <v>20.929</v>
-      </c>
-      <c r="AM52" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>202:40</t>
-        </is>
-      </c>
-      <c r="AO52" t="n">
-        <v>88.724</v>
-      </c>
-      <c r="AP52" t="n">
-        <v>0.531</v>
-      </c>
-      <c r="AQ52" t="n">
-        <v>0.578</v>
-      </c>
-      <c r="AR52" t="n">
-        <v>0.974</v>
-      </c>
-      <c r="AS52" t="n">
-        <v>0.157</v>
-      </c>
-      <c r="AT52" t="n">
-        <v>0.271</v>
-      </c>
-      <c r="AU52" t="n">
-        <v>1.279</v>
-      </c>
-      <c r="AV52" t="n">
-        <v>0.203</v>
-      </c>
-      <c r="AW52" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="AX52" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="AY52" t="n">
         <v>0</v>
       </c>
     </row>

--- a/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Surne Bilbao Basket.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Surne Bilbao Basket.xlsx
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2491.92</v>
+        <v>2641.84</v>
       </c>
       <c r="C2" t="n">
-        <v>2497.84</v>
+        <v>2648.5</v>
       </c>
       <c r="D2" t="n">
-        <v>108.5337731800275</v>
+        <v>108.8918255616387</v>
       </c>
       <c r="E2" t="n">
-        <v>110.5755372641963</v>
+        <v>110.4021144043798</v>
       </c>
       <c r="F2" t="n">
-        <v>0.528169014084507</v>
+        <v>0.5300859598853869</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1608337622233659</v>
+        <v>0.1616692092721848</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2688927943760984</v>
+        <v>0.2686192468619247</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3073440643863179</v>
+        <v>0.3170964660936008</v>
       </c>
       <c r="J2" t="n">
-        <v>376</v>
+        <v>404</v>
       </c>
       <c r="K2" t="n">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="L2" t="n">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="M2" t="n">
-        <v>417</v>
+        <v>444</v>
       </c>
       <c r="N2" t="n">
-        <v>1008</v>
+        <v>1085</v>
       </c>
       <c r="O2" t="n">
-        <v>1415</v>
+        <v>1511</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7117706237424547</v>
+        <v>0.721585482330468</v>
       </c>
       <c r="Q2" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="R2" t="n">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1388329979879276</v>
+        <v>0.1380133715377268</v>
       </c>
       <c r="T2" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="U2" t="n">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1242454728370221</v>
+        <v>0.1217765042979943</v>
       </c>
       <c r="W2" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="X2" t="n">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.08702213279678069</v>
+        <v>0.09025787965616046</v>
       </c>
       <c r="Z2" t="n">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="AA2" t="n">
-        <v>695</v>
+        <v>736</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3495975855130785</v>
+        <v>0.3514804202483285</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.7123674911660778</v>
+        <v>0.7180675049636003</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.4130434782608696</v>
+        <v>0.4048442906574394</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.3603238866396761</v>
+        <v>0.3607843137254902</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.4046242774566474</v>
+        <v>0.3968253968253968</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3309352517985611</v>
+        <v>0.3328804347826087</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.424734982332156</v>
+        <v>1.436135009927201</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.7206477732793523</v>
+        <v>0.7215686274509804</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.036866359447005</v>
+        <v>1.037837837837838</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.8487584650112867</v>
+        <v>0.8595744680851064</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.8921568627450981</v>
+        <v>0.8909657320872274</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.753086419753086</v>
+        <v>1.741573033707865</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.197777777777778</v>
+        <v>1.196242171189979</v>
       </c>
       <c r="AO2" t="n">
-        <v>4.417777777777777</v>
+        <v>4.37160751565762</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.615555555555556</v>
+        <v>5.567849686847599</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>77.8725</v>
+        <v>77.70117647058824</v>
       </c>
       <c r="C3" t="n">
-        <v>78.0575</v>
+        <v>77.89705882352941</v>
       </c>
       <c r="D3" t="n">
-        <v>108.5337731800275</v>
+        <v>108.8918255616387</v>
       </c>
       <c r="E3" t="n">
-        <v>110.5755372641963</v>
+        <v>110.4021144043798</v>
       </c>
       <c r="F3" t="n">
-        <v>0.528169014084507</v>
+        <v>0.5300859598853868</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1608337622233659</v>
+        <v>0.1616692092721848</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2688927943760984</v>
+        <v>0.2686192468619247</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3073440643863179</v>
+        <v>0.3170964660936008</v>
       </c>
       <c r="J3" t="n">
-        <v>11.75</v>
+        <v>11.88235294117647</v>
       </c>
       <c r="K3" t="n">
-        <v>8.53125</v>
+        <v>8.411764705882353</v>
       </c>
       <c r="L3" t="n">
-        <v>4.4375</v>
+        <v>4.558823529411764</v>
       </c>
       <c r="M3" t="n">
-        <v>13.03125</v>
+        <v>13.05882352941176</v>
       </c>
       <c r="N3" t="n">
-        <v>31.5</v>
+        <v>31.91176470588235</v>
       </c>
       <c r="O3" t="n">
-        <v>44.21875</v>
+        <v>44.44117647058823</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7117706237424547</v>
+        <v>0.7215854823304679</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.5625</v>
+        <v>3.441176470588236</v>
       </c>
       <c r="R3" t="n">
-        <v>8.625</v>
+        <v>8.5</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1388329979879276</v>
+        <v>0.1380133715377268</v>
       </c>
       <c r="T3" t="n">
-        <v>2.78125</v>
+        <v>2.705882352941177</v>
       </c>
       <c r="U3" t="n">
-        <v>7.71875</v>
+        <v>7.5</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1242454728370221</v>
+        <v>0.1217765042979943</v>
       </c>
       <c r="W3" t="n">
-        <v>2.1875</v>
+        <v>2.205882352941177</v>
       </c>
       <c r="X3" t="n">
-        <v>5.40625</v>
+        <v>5.558823529411764</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.08702213279678069</v>
+        <v>0.09025787965616044</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.1875</v>
+        <v>7.205882352941177</v>
       </c>
       <c r="AA3" t="n">
-        <v>21.71875</v>
+        <v>21.64705882352941</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3495975855130785</v>
+        <v>0.3514804202483285</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.7123674911660778</v>
+        <v>0.7180675049636003</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.4130434782608696</v>
+        <v>0.4048442906574395</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.3603238866396761</v>
+        <v>0.3607843137254902</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.4046242774566474</v>
+        <v>0.3968253968253969</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3309352517985611</v>
+        <v>0.3328804347826087</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.424734982332156</v>
+        <v>1.436135009927201</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.7206477732793523</v>
+        <v>0.7215686274509804</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.036866359447005</v>
+        <v>1.037837837837838</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.8487584650112867</v>
+        <v>0.8595744680851064</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.8921568627450981</v>
+        <v>0.8909657320872274</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.753086419753086</v>
+        <v>1.741573033707865</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.197777777777778</v>
+        <v>1.196242171189979</v>
       </c>
       <c r="AO3" t="n">
-        <v>4.417777777777777</v>
+        <v>4.371607515657621</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.615555555555556</v>
+        <v>5.567849686847599</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2503.76</v>
+        <v>2655.16</v>
       </c>
       <c r="C4" t="n">
-        <v>2497.84</v>
+        <v>2648.5</v>
       </c>
       <c r="D4" t="n">
-        <v>110.5755372641963</v>
+        <v>110.4021144043798</v>
       </c>
       <c r="E4" t="n">
-        <v>108.5337731800275</v>
+        <v>108.8918255616387</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5316731141199227</v>
+        <v>0.5285326086956522</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1564398112834421</v>
+        <v>0.1559306738859251</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2879719051799824</v>
+        <v>0.2945036915504512</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2722437137330754</v>
+        <v>0.2672101449275363</v>
       </c>
       <c r="J4" t="n">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="K4" t="n">
-        <v>337</v>
+        <v>362</v>
       </c>
       <c r="L4" t="n">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="M4" t="n">
-        <v>406</v>
+        <v>431</v>
       </c>
       <c r="N4" t="n">
-        <v>971</v>
+        <v>1025</v>
       </c>
       <c r="O4" t="n">
-        <v>1337</v>
+        <v>1410</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6465183752417795</v>
+        <v>0.6385869565217391</v>
       </c>
       <c r="Q4" t="n">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="R4" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1615087040618955</v>
+        <v>0.1585144927536232</v>
       </c>
       <c r="T4" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="U4" t="n">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1242746615087041</v>
+        <v>0.1268115942028986</v>
       </c>
       <c r="W4" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="X4" t="n">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.08752417794970986</v>
+        <v>0.08605072463768115</v>
       </c>
       <c r="Z4" t="n">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="AA4" t="n">
-        <v>688</v>
+        <v>742</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3326885880077369</v>
+        <v>0.3360507246376812</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.7262528047868362</v>
+        <v>0.7269503546099291</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.4431137724550898</v>
+        <v>0.44</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.3813229571984436</v>
+        <v>0.3714285714285714</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.3535911602209945</v>
+        <v>0.3473684210526316</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3386627906976744</v>
+        <v>0.3369272237196765</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.452505609573672</v>
+        <v>1.453900709219858</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.7626459143968871</v>
+        <v>0.7428571428571429</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.025316455696202</v>
+        <v>1.017167381974249</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.8111111111111111</v>
+        <v>0.791231732776618</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.027439024390244</v>
+        <v>1.008356545961003</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.613445378151261</v>
+        <v>1.612903225806452</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.284424379232506</v>
+        <v>1.276595744680851</v>
       </c>
       <c r="AO4" t="n">
-        <v>4.668171557562077</v>
+        <v>4.697872340425532</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.952595936794582</v>
+        <v>5.974468085106383</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>78.24250000000001</v>
+        <v>78.0929411764706</v>
       </c>
       <c r="C5" t="n">
-        <v>78.0575</v>
+        <v>77.89705882352941</v>
       </c>
       <c r="D5" t="n">
-        <v>110.5755372641963</v>
+        <v>110.4021144043798</v>
       </c>
       <c r="E5" t="n">
-        <v>108.5337731800275</v>
+        <v>108.8918255616387</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5316731141199227</v>
+        <v>0.5285326086956522</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1564398112834421</v>
+        <v>0.1559306738859251</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2879719051799824</v>
+        <v>0.2945036915504512</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2722437137330754</v>
+        <v>0.2672101449275363</v>
       </c>
       <c r="J5" t="n">
-        <v>11.40625</v>
+        <v>11.14705882352941</v>
       </c>
       <c r="K5" t="n">
-        <v>10.53125</v>
+        <v>10.64705882352941</v>
       </c>
       <c r="L5" t="n">
-        <v>6</v>
+        <v>5.882352941176471</v>
       </c>
       <c r="M5" t="n">
-        <v>12.6875</v>
+        <v>12.67647058823529</v>
       </c>
       <c r="N5" t="n">
-        <v>30.34375</v>
+        <v>30.14705882352941</v>
       </c>
       <c r="O5" t="n">
-        <v>41.78125</v>
+        <v>41.47058823529412</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6465183752417795</v>
+        <v>0.6385869565217391</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.625</v>
+        <v>4.529411764705882</v>
       </c>
       <c r="R5" t="n">
-        <v>10.4375</v>
+        <v>10.29411764705882</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1615087040618955</v>
+        <v>0.1585144927536232</v>
       </c>
       <c r="T5" t="n">
-        <v>3.0625</v>
+        <v>3.058823529411764</v>
       </c>
       <c r="U5" t="n">
-        <v>8.03125</v>
+        <v>8.235294117647058</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1242746615087041</v>
+        <v>0.1268115942028985</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>1.941176470588235</v>
       </c>
       <c r="X5" t="n">
-        <v>5.65625</v>
+        <v>5.588235294117647</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.08752417794970986</v>
+        <v>0.08605072463768115</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.28125</v>
+        <v>7.352941176470588</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.5</v>
+        <v>21.82352941176471</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3326885880077369</v>
+        <v>0.3360507246376812</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.7262528047868362</v>
+        <v>0.7269503546099292</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.4431137724550898</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.3813229571984436</v>
+        <v>0.3714285714285714</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.3535911602209945</v>
+        <v>0.3473684210526316</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3386627906976744</v>
+        <v>0.3369272237196765</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.452505609573672</v>
+        <v>1.453900709219858</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.7626459143968871</v>
+        <v>0.7428571428571429</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.025316455696202</v>
+        <v>1.017167381974249</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.8111111111111111</v>
+        <v>0.791231732776618</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.027439024390244</v>
+        <v>1.008356545961003</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.613445378151261</v>
+        <v>1.612903225806452</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.284424379232506</v>
+        <v>1.276595744680851</v>
       </c>
       <c r="AO5" t="n">
-        <v>4.668171557562077</v>
+        <v>4.697872340425532</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.952595936794582</v>
+        <v>5.974468085106383</v>
       </c>
     </row>
     <row r="7">
@@ -1419,40 +1419,40 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>34</v>
+      </c>
+      <c r="C8" t="n">
+        <v>267</v>
+      </c>
+      <c r="D8" t="n">
+        <v>56</v>
+      </c>
+      <c r="E8" t="n">
+        <v>112</v>
+      </c>
+      <c r="F8" t="n">
+        <v>34</v>
+      </c>
+      <c r="G8" t="n">
+        <v>122</v>
+      </c>
+      <c r="H8" t="n">
+        <v>53</v>
+      </c>
+      <c r="I8" t="n">
+        <v>73</v>
+      </c>
+      <c r="J8" t="n">
+        <v>61</v>
+      </c>
+      <c r="K8" t="n">
+        <v>58</v>
+      </c>
+      <c r="L8" t="n">
+        <v>18</v>
+      </c>
+      <c r="M8" t="n">
         <v>32</v>
-      </c>
-      <c r="C8" t="n">
-        <v>251</v>
-      </c>
-      <c r="D8" t="n">
-        <v>53</v>
-      </c>
-      <c r="E8" t="n">
-        <v>108</v>
-      </c>
-      <c r="F8" t="n">
-        <v>31</v>
-      </c>
-      <c r="G8" t="n">
-        <v>115</v>
-      </c>
-      <c r="H8" t="n">
-        <v>52</v>
-      </c>
-      <c r="I8" t="n">
-        <v>71</v>
-      </c>
-      <c r="J8" t="n">
-        <v>58</v>
-      </c>
-      <c r="K8" t="n">
-        <v>54</v>
-      </c>
-      <c r="L8" t="n">
-        <v>17</v>
-      </c>
-      <c r="M8" t="n">
-        <v>28</v>
       </c>
       <c r="N8" t="n">
         <v>11</v>
@@ -1461,25 +1461,25 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="Q8" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="R8" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="S8" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="T8" t="n">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="U8" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="V8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="W8" t="n">
         <v>18</v>
@@ -1488,78 +1488,78 @@
         <v>11</v>
       </c>
       <c r="Y8" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="Z8" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.679</v>
+        <v>0.681</v>
       </c>
       <c r="AB8" t="n">
         <v>19</v>
       </c>
       <c r="AC8" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.487</v>
+        <v>0.475</v>
       </c>
       <c r="AE8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AF8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.357</v>
+        <v>0.379</v>
       </c>
       <c r="AH8" t="n">
         <v>3</v>
       </c>
       <c r="AI8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.176</v>
+        <v>0.158</v>
       </c>
       <c r="AK8" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="AL8" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.286</v>
+        <v>0.301</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>645:43</t>
+          <t>685:45</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>296.24</v>
+        <v>312.12</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.446</v>
+        <v>0.457</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.494</v>
+        <v>0.502</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.847</v>
+        <v>0.855</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.142</v>
+        <v>0.147</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.233</v>
+        <v>0.226</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.381</v>
+        <v>1.326</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.212</v>
+        <v>0.211</v>
       </c>
       <c r="AW8" t="n">
         <v>0.03</v>
@@ -1578,22 +1578,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D9" t="n">
         <v>39</v>
       </c>
       <c r="E9" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G9" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H9" t="n">
         <v>65</v>
@@ -1602,10 +1602,10 @@
         <v>76</v>
       </c>
       <c r="J9" t="n">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K9" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L9" t="n">
         <v>8</v>
@@ -1626,13 +1626,13 @@
         <v>31</v>
       </c>
       <c r="R9" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="S9" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="T9" t="n">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="U9" t="n">
         <v>28</v>
@@ -1641,37 +1641,37 @@
         <v>14</v>
       </c>
       <c r="W9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="X9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y9" t="n">
         <v>82</v>
       </c>
       <c r="Z9" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.788</v>
+        <v>0.781</v>
       </c>
       <c r="AB9" t="n">
         <v>12</v>
       </c>
       <c r="AC9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.706</v>
+        <v>0.667</v>
       </c>
       <c r="AE9" t="n">
         <v>10</v>
       </c>
       <c r="AF9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.435</v>
+        <v>0.417</v>
       </c>
       <c r="AH9" t="n">
         <v>5</v>
@@ -1683,51 +1683,51 @@
         <v>0.385</v>
       </c>
       <c r="AK9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL9" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.258</v>
+        <v>0.257</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>506:23</t>
+          <t>534:49</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>211.44</v>
+        <v>218.44</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.49</v>
+        <v>0.477</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.579</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.988</v>
+        <v>0.971</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.147</v>
+        <v>0.142</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.442</v>
+        <v>0.422</v>
       </c>
       <c r="AU9" t="n">
-        <v>2.484</v>
+        <v>2.774</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.193</v>
+        <v>0.19</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
       <c r="AX9" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.092</v>
+        <v>0.097</v>
       </c>
     </row>
     <row r="10">
@@ -2214,40 +2214,40 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C13" t="n">
-        <v>412</v>
+        <v>432</v>
       </c>
       <c r="D13" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E13" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="F13" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G13" t="n">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="H13" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="I13" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="J13" t="n">
         <v>41</v>
       </c>
       <c r="K13" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N13" t="n">
         <v>19</v>
@@ -2256,114 +2256,114 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Q13" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R13" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="S13" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="T13" t="n">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="U13" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="V13" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="W13" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="X13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y13" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="Z13" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.781</v>
+        <v>0.785</v>
       </c>
       <c r="AB13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AC13" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.303</v>
+        <v>0.314</v>
       </c>
       <c r="AE13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AF13" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.354</v>
+        <v>0.353</v>
       </c>
       <c r="AH13" t="n">
         <v>14</v>
       </c>
       <c r="AI13" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.378</v>
+        <v>0.359</v>
       </c>
       <c r="AK13" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="AL13" t="n">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.38</v>
+        <v>0.377</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>732:28</t>
+          <t>776:52</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>426.4</v>
+        <v>447.04</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.5</v>
+        <v>0.497</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.552</v>
+        <v>0.55</v>
       </c>
       <c r="AR13" t="n">
         <v>0.966</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.124</v>
+        <v>0.121</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.226</v>
+        <v>0.229</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.774</v>
+        <v>0.759</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.269</v>
+        <v>0.267</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.051</v>
+        <v>0.049</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.053</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="14">
@@ -2691,37 +2691,37 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C16" t="n">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
       </c>
       <c r="E16" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F16" t="n">
         <v>29</v>
       </c>
       <c r="G16" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H16" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="I16" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="J16" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K16" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="L16" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M16" t="n">
         <v>23</v>
@@ -2733,25 +2733,25 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q16" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="R16" t="n">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="S16" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="T16" t="n">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="U16" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="V16" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="W16" t="n">
         <v>15</v>
@@ -2760,22 +2760,22 @@
         <v>8</v>
       </c>
       <c r="Y16" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="Z16" t="n">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.748</v>
+        <v>0.752</v>
       </c>
       <c r="AB16" t="n">
         <v>3</v>
       </c>
       <c r="AC16" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.273</v>
+        <v>0.231</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -2790,57 +2790,57 @@
         <v>7</v>
       </c>
       <c r="AI16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.412</v>
+        <v>0.389</v>
       </c>
       <c r="AK16" t="n">
         <v>22</v>
       </c>
       <c r="AL16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.449</v>
+        <v>0.44</v>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>593:52</t>
+          <t>624:27</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>231.32</v>
+        <v>239.96</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.65</v>
+        <v>0.635</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.681</v>
+        <v>0.671</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.185</v>
+        <v>1.163</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.13</v>
+        <v>0.133</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.341</v>
+        <v>0.363</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.906</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.18</v>
+        <v>0.178</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.052</v>
+        <v>0.053</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.155</v>
+        <v>0.154</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.035</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="17">
@@ -2850,67 +2850,67 @@
         </is>
       </c>
       <c r="B17" t="n">
+        <v>32</v>
+      </c>
+      <c r="C17" t="n">
+        <v>407</v>
+      </c>
+      <c r="D17" t="n">
+        <v>74</v>
+      </c>
+      <c r="E17" t="n">
+        <v>157</v>
+      </c>
+      <c r="F17" t="n">
+        <v>56</v>
+      </c>
+      <c r="G17" t="n">
+        <v>173</v>
+      </c>
+      <c r="H17" t="n">
+        <v>91</v>
+      </c>
+      <c r="I17" t="n">
+        <v>111</v>
+      </c>
+      <c r="J17" t="n">
+        <v>86</v>
+      </c>
+      <c r="K17" t="n">
+        <v>76</v>
+      </c>
+      <c r="L17" t="n">
+        <v>19</v>
+      </c>
+      <c r="M17" t="n">
         <v>30</v>
       </c>
-      <c r="C17" t="n">
-        <v>379</v>
-      </c>
-      <c r="D17" t="n">
+      <c r="N17" t="n">
+        <v>13</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>79</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>79</v>
+      </c>
+      <c r="R17" t="n">
         <v>72</v>
       </c>
-      <c r="E17" t="n">
-        <v>151</v>
-      </c>
-      <c r="F17" t="n">
-        <v>51</v>
-      </c>
-      <c r="G17" t="n">
-        <v>164</v>
-      </c>
-      <c r="H17" t="n">
-        <v>82</v>
-      </c>
-      <c r="I17" t="n">
-        <v>100</v>
-      </c>
-      <c r="J17" t="n">
-        <v>80</v>
-      </c>
-      <c r="K17" t="n">
-        <v>73</v>
-      </c>
-      <c r="L17" t="n">
-        <v>18</v>
-      </c>
-      <c r="M17" t="n">
-        <v>29</v>
-      </c>
-      <c r="N17" t="n">
-        <v>12</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>72</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>72</v>
-      </c>
-      <c r="R17" t="n">
-        <v>67</v>
-      </c>
       <c r="S17" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="T17" t="n">
-        <v>318</v>
+        <v>344</v>
       </c>
       <c r="U17" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="V17" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="W17" t="n">
         <v>18</v>
@@ -2919,10 +2919,10 @@
         <v>8</v>
       </c>
       <c r="Y17" t="n">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="Z17" t="n">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="AA17" t="n">
         <v>0.739</v>
@@ -2931,10 +2931,10 @@
         <v>18</v>
       </c>
       <c r="AC17" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.375</v>
+        <v>0.36</v>
       </c>
       <c r="AE17" t="n">
         <v>14</v>
@@ -2946,60 +2946,60 @@
         <v>0.368</v>
       </c>
       <c r="AH17" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AI17" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.364</v>
+        <v>0.44</v>
       </c>
       <c r="AK17" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="AL17" t="n">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.303</v>
+        <v>0.304</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>717:56</t>
+          <t>768:15</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>431</v>
+        <v>457.84</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.471</v>
+        <v>0.479</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.528</v>
+        <v>0.537</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.879</v>
+        <v>0.889</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.167</v>
+        <v>0.173</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.26</v>
+        <v>0.276</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.111</v>
+        <v>1.089</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.278</v>
+        <v>0.277</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.029</v>
+        <v>0.028</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.116</v>
+        <v>0.112</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.103</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="18">
@@ -3168,16 +3168,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C19" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E19" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F19" t="n">
         <v>2</v>
@@ -3189,40 +3189,40 @@
         <v>30</v>
       </c>
       <c r="I19" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J19" t="n">
         <v>10</v>
       </c>
       <c r="K19" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="L19" t="n">
         <v>36</v>
       </c>
       <c r="M19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R19" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="S19" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="T19" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="U19" t="n">
         <v>12</v>
@@ -3231,19 +3231,19 @@
         <v>17</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="Z19" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.713</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="AB19" t="n">
         <v>6</v>
@@ -3283,41 +3283,41 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>375:52</t>
+          <t>395:35</t>
         </is>
       </c>
       <c r="AO19" t="n">
-        <v>117.48</v>
+        <v>122.24</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.597</v>
+        <v>0.608</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.641</v>
+        <v>0.637</v>
       </c>
       <c r="AR19" t="n">
-        <v>0.987</v>
+        <v>0.982</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.23</v>
+        <v>0.229</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.417</v>
+        <v>0.405</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.37</v>
+        <v>0.357</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.145</v>
+        <v>0.143</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.109</v>
+        <v>0.105</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.2</v>
+        <v>0.194</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="20">
@@ -3327,40 +3327,40 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C20" t="n">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="D20" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E20" t="n">
+        <v>81</v>
+      </c>
+      <c r="F20" t="n">
+        <v>39</v>
+      </c>
+      <c r="G20" t="n">
+        <v>107</v>
+      </c>
+      <c r="H20" t="n">
+        <v>36</v>
+      </c>
+      <c r="I20" t="n">
+        <v>44</v>
+      </c>
+      <c r="J20" t="n">
+        <v>29</v>
+      </c>
+      <c r="K20" t="n">
         <v>78</v>
       </c>
-      <c r="F20" t="n">
-        <v>36</v>
-      </c>
-      <c r="G20" t="n">
-        <v>97</v>
-      </c>
-      <c r="H20" t="n">
-        <v>32</v>
-      </c>
-      <c r="I20" t="n">
-        <v>40</v>
-      </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
         <v>28</v>
       </c>
-      <c r="K20" t="n">
-        <v>70</v>
-      </c>
-      <c r="L20" t="n">
-        <v>27</v>
-      </c>
       <c r="M20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N20" t="n">
         <v>9</v>
@@ -3369,19 +3369,19 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="Q20" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R20" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="S20" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="T20" t="n">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="U20" t="n">
         <v>43</v>
@@ -3396,13 +3396,13 @@
         <v>8</v>
       </c>
       <c r="Y20" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="Z20" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.779</v>
+        <v>0.783</v>
       </c>
       <c r="AB20" t="n">
         <v>4</v>
@@ -3414,66 +3414,66 @@
         <v>0.235</v>
       </c>
       <c r="AE20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.4</v>
+        <v>0.438</v>
       </c>
       <c r="AH20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI20" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.471</v>
+        <v>0.447</v>
       </c>
       <c r="AK20" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AL20" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.317</v>
+        <v>0.319</v>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>676:11</t>
+          <t>723:15</t>
         </is>
       </c>
       <c r="AO20" t="n">
-        <v>221.6</v>
+        <v>238.36</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.597</v>
+        <v>0.596</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.038</v>
+        <v>1.036</v>
       </c>
       <c r="AS20" t="n">
-        <v>0.131</v>
+        <v>0.13</v>
       </c>
       <c r="AT20" t="n">
-        <v>0.183</v>
+        <v>0.191</v>
       </c>
       <c r="AU20" t="n">
-        <v>0.966</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.152</v>
+        <v>0.153</v>
       </c>
       <c r="AW20" t="n">
         <v>0.045</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.118</v>
+        <v>0.122</v>
       </c>
       <c r="AY20" t="n">
         <v>0.034</v>
@@ -3486,40 +3486,40 @@
         </is>
       </c>
       <c r="B21" t="n">
+        <v>34</v>
+      </c>
+      <c r="C21" t="n">
+        <v>376</v>
+      </c>
+      <c r="D21" t="n">
+        <v>71</v>
+      </c>
+      <c r="E21" t="n">
+        <v>158</v>
+      </c>
+      <c r="F21" t="n">
         <v>32</v>
       </c>
-      <c r="C21" t="n">
-        <v>341</v>
-      </c>
-      <c r="D21" t="n">
-        <v>65</v>
-      </c>
-      <c r="E21" t="n">
-        <v>148</v>
-      </c>
-      <c r="F21" t="n">
-        <v>31</v>
-      </c>
       <c r="G21" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="H21" t="n">
+        <v>138</v>
+      </c>
+      <c r="I21" t="n">
+        <v>174</v>
+      </c>
+      <c r="J21" t="n">
+        <v>140</v>
+      </c>
+      <c r="K21" t="n">
         <v>118</v>
       </c>
-      <c r="I21" t="n">
-        <v>150</v>
-      </c>
-      <c r="J21" t="n">
-        <v>132</v>
-      </c>
-      <c r="K21" t="n">
-        <v>112</v>
-      </c>
       <c r="L21" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M21" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N21" t="n">
         <v>15</v>
@@ -3528,114 +3528,114 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="Q21" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="R21" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="S21" t="n">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="T21" t="n">
-        <v>550</v>
+        <v>596</v>
       </c>
       <c r="U21" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="V21" t="n">
         <v>17</v>
       </c>
       <c r="W21" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="X21" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Y21" t="n">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="Z21" t="n">
-        <v>223</v>
+        <v>252</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.7</v>
+        <v>0.718</v>
       </c>
       <c r="AB21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AC21" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.316</v>
+        <v>0.317</v>
       </c>
       <c r="AE21" t="n">
         <v>15</v>
       </c>
       <c r="AF21" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.405</v>
+        <v>0.385</v>
       </c>
       <c r="AH21" t="n">
         <v>6</v>
       </c>
       <c r="AI21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.75</v>
+        <v>0.667</v>
       </c>
       <c r="AK21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL21" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.455</v>
+        <v>0.433</v>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>769:49</t>
+          <t>821:50</t>
         </is>
       </c>
       <c r="AO21" t="n">
-        <v>334</v>
+        <v>363.56</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.528</v>
+        <v>0.524</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.616</v>
+        <v>0.619</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.021</v>
+        <v>1.034</v>
       </c>
       <c r="AS21" t="n">
-        <v>0.171</v>
+        <v>0.165</v>
       </c>
       <c r="AT21" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.608</v>
       </c>
       <c r="AU21" t="n">
-        <v>2.316</v>
+        <v>2.333</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.201</v>
+        <v>0.205</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.031</v>
+        <v>0.032</v>
       </c>
       <c r="AX21" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="AY21" t="n">
         <v>0.165</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>0.164</v>
       </c>
     </row>
     <row r="22">
@@ -3645,7 +3645,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C22" t="n">
         <v>29</v>
@@ -3672,7 +3672,7 @@
         <v>2</v>
       </c>
       <c r="K22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L22" t="n">
         <v>8</v>
@@ -3699,7 +3699,7 @@
         <v>8</v>
       </c>
       <c r="T22" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="U22" t="n">
         <v>5</v>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>108:38</t>
+          <t>113:05</t>
         </is>
       </c>
       <c r="AO22" t="n">
@@ -3785,13 +3785,13 @@
         <v>1</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.123</v>
+        <v>0.118</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.081</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.178</v>
+        <v>0.18</v>
       </c>
       <c r="AY22" t="n">
         <v>0.002</v>
@@ -3804,40 +3804,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C23" t="n">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="D23" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E23" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F23" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G23" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J23" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L23" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M23" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N23" t="n">
         <v>6</v>
@@ -3846,40 +3846,40 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Q23" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="R23" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T23" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="U23" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="V23" t="n">
         <v>9</v>
       </c>
       <c r="W23" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="X23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y23" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z23" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.533</v>
+        <v>0.632</v>
       </c>
       <c r="AB23" t="n">
         <v>7</v>
@@ -3900,60 +3900,60 @@
         <v>0.4</v>
       </c>
       <c r="AH23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI23" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.455</v>
+        <v>0.44</v>
       </c>
       <c r="AK23" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AL23" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.258</v>
+        <v>0.306</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>257:20</t>
+          <t>282:43</t>
         </is>
       </c>
       <c r="AO23" t="n">
-        <v>91.88</v>
+        <v>106.76</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.524</v>
+        <v>0.554</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.525</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR23" t="n">
-        <v>0.947</v>
+        <v>0.984</v>
       </c>
       <c r="AS23" t="n">
-        <v>0.098</v>
+        <v>0.122</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.012</v>
+        <v>0.033</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.222</v>
+        <v>1.077</v>
       </c>
       <c r="AV23" t="n">
-        <v>0.165</v>
+        <v>0.175</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.044</v>
+        <v>0.049</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.062</v>
+        <v>0.06</v>
       </c>
       <c r="AY23" t="n">
-        <v>0.013</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="24">
@@ -3963,16 +3963,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C24" t="n">
-        <v>316</v>
+        <v>343</v>
       </c>
       <c r="D24" t="n">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="E24" t="n">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -3981,73 +3981,73 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="I24" t="n">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="J24" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K24" t="n">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="L24" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="M24" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N24" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="Q24" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="R24" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="S24" t="n">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="T24" t="n">
-        <v>527</v>
+        <v>579</v>
       </c>
       <c r="U24" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="V24" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="W24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y24" t="n">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="Z24" t="n">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.658</v>
+        <v>0.672</v>
       </c>
       <c r="AB24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AC24" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.429</v>
+        <v>0.432</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -4078,38 +4078,38 @@
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>747:47</t>
+          <t>802:46</t>
         </is>
       </c>
       <c r="AO24" t="n">
-        <v>284</v>
+        <v>301.96</v>
       </c>
       <c r="AP24" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AQ24" t="n">
         <v>0.6860000000000001</v>
       </c>
-      <c r="AQ24" t="n">
-        <v>0.672</v>
-      </c>
       <c r="AR24" t="n">
-        <v>1.113</v>
+        <v>1.136</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.173</v>
+        <v>0.172</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.497</v>
+        <v>0.506</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.122</v>
+        <v>1.115</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.176</v>
+        <v>0.175</v>
       </c>
       <c r="AW24" t="n">
-        <v>0.107</v>
+        <v>0.106</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.213</v>
+        <v>0.215</v>
       </c>
       <c r="AY24" t="n">
         <v>0.07000000000000001</v>
@@ -4122,7 +4122,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C25" t="n">
         <v>67</v>
@@ -4149,10 +4149,10 @@
         <v>17</v>
       </c>
       <c r="K25" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M25" t="n">
         <v>10</v>
@@ -4170,7 +4170,7 @@
         <v>16</v>
       </c>
       <c r="R25" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="S25" t="n">
         <v>18</v>
@@ -4237,7 +4237,7 @@
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>354:48</t>
+          <t>358:15</t>
         </is>
       </c>
       <c r="AO25" t="n">
@@ -4265,13 +4265,13 @@
         <v>0.118</v>
       </c>
       <c r="AW25" t="n">
-        <v>0.067</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AX25" t="n">
-        <v>0.16</v>
+        <v>0.161</v>
       </c>
       <c r="AY25" t="n">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="26">
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -4308,7 +4308,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="L26" t="n">
         <v>36</v>
@@ -4323,7 +4323,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4440,144 +4440,144 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C27" t="n">
-        <v>2711</v>
+        <v>2884</v>
       </c>
       <c r="D27" t="n">
-        <v>600</v>
+        <v>630</v>
       </c>
       <c r="E27" t="n">
-        <v>1120</v>
+        <v>1169</v>
       </c>
       <c r="F27" t="n">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="G27" t="n">
-        <v>868</v>
+        <v>925</v>
       </c>
       <c r="H27" t="n">
-        <v>611</v>
+        <v>664</v>
       </c>
       <c r="I27" t="n">
-        <v>818</v>
+        <v>886</v>
       </c>
       <c r="J27" t="n">
-        <v>539</v>
+        <v>573</v>
       </c>
       <c r="K27" t="n">
-        <v>811</v>
+        <v>860</v>
       </c>
       <c r="L27" t="n">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="M27" t="n">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="N27" t="n">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>450</v>
+        <v>479</v>
       </c>
       <c r="Q27" t="n">
-        <v>417</v>
+        <v>444</v>
       </c>
       <c r="R27" t="n">
-        <v>724</v>
+        <v>765</v>
       </c>
       <c r="S27" t="n">
-        <v>737</v>
+        <v>790</v>
       </c>
       <c r="T27" t="n">
-        <v>3038</v>
+        <v>3238</v>
       </c>
       <c r="U27" t="n">
-        <v>376</v>
+        <v>404</v>
       </c>
       <c r="V27" t="n">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="W27" t="n">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="X27" t="n">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="Y27" t="n">
-        <v>1008</v>
+        <v>1085</v>
       </c>
       <c r="Z27" t="n">
-        <v>1415</v>
+        <v>1511</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.712</v>
+        <v>0.718</v>
       </c>
       <c r="AB27" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AC27" t="n">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.413</v>
+        <v>0.405</v>
       </c>
       <c r="AE27" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="AF27" t="n">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.36</v>
+        <v>0.361</v>
       </c>
       <c r="AH27" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AI27" t="n">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.405</v>
+        <v>0.397</v>
       </c>
       <c r="AK27" t="n">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="AL27" t="n">
-        <v>695</v>
+        <v>736</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.331</v>
+        <v>0.333</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>6475:00</t>
+          <t>6875:00</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>2797.92</v>
+        <v>2962.84</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.528</v>
+        <v>0.53</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.577</v>
+        <v>0.581</v>
       </c>
       <c r="AR27" t="n">
-        <v>0.969</v>
+        <v>0.973</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.161</v>
+        <v>0.162</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.307</v>
+        <v>0.317</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.198</v>
+        <v>1.196</v>
       </c>
       <c r="AV27" t="n">
         <v>0.2</v>
@@ -4586,7 +4586,7 @@
         <v>0.054</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.142</v>
+        <v>0.141</v>
       </c>
       <c r="AY27" t="n">
         <v>0</v>
@@ -4599,150 +4599,150 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C28" t="n">
-        <v>2762</v>
+        <v>2924</v>
       </c>
       <c r="D28" t="n">
-        <v>654</v>
+        <v>693</v>
       </c>
       <c r="E28" t="n">
-        <v>1199</v>
+        <v>1276</v>
       </c>
       <c r="F28" t="n">
-        <v>297</v>
+        <v>316</v>
       </c>
       <c r="G28" t="n">
-        <v>869</v>
+        <v>932</v>
       </c>
       <c r="H28" t="n">
-        <v>563</v>
+        <v>590</v>
       </c>
       <c r="I28" t="n">
-        <v>729</v>
+        <v>764</v>
       </c>
       <c r="J28" t="n">
-        <v>569</v>
+        <v>600</v>
       </c>
       <c r="K28" t="n">
-        <v>832</v>
+        <v>874</v>
       </c>
       <c r="L28" t="n">
-        <v>328</v>
+        <v>359</v>
       </c>
       <c r="M28" t="n">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="N28" t="n">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>443</v>
+        <v>470</v>
       </c>
       <c r="Q28" t="n">
-        <v>406</v>
+        <v>431</v>
       </c>
       <c r="R28" t="n">
-        <v>747</v>
+        <v>800</v>
       </c>
       <c r="S28" t="n">
-        <v>715</v>
+        <v>755</v>
       </c>
       <c r="T28" t="n">
-        <v>3154</v>
+        <v>3307</v>
       </c>
       <c r="U28" t="n">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="V28" t="n">
-        <v>337</v>
+        <v>362</v>
       </c>
       <c r="W28" t="n">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="X28" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="Y28" t="n">
-        <v>971</v>
+        <v>1025</v>
       </c>
       <c r="Z28" t="n">
-        <v>1337</v>
+        <v>1410</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.726</v>
+        <v>0.727</v>
       </c>
       <c r="AB28" t="n">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="AC28" t="n">
-        <v>334</v>
+        <v>350</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.443</v>
+        <v>0.44</v>
       </c>
       <c r="AE28" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="AF28" t="n">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.381</v>
+        <v>0.371</v>
       </c>
       <c r="AH28" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="AI28" t="n">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.354</v>
+        <v>0.347</v>
       </c>
       <c r="AK28" t="n">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="AL28" t="n">
-        <v>688</v>
+        <v>742</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.339</v>
+        <v>0.337</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>6475:00</t>
+          <t>6875:00</t>
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>2831.76</v>
+        <v>3014.16</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.532</v>
+        <v>0.529</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.578</v>
+        <v>0.575</v>
       </c>
       <c r="AR28" t="n">
-        <v>0.975</v>
+        <v>0.97</v>
       </c>
       <c r="AS28" t="n">
         <v>0.156</v>
       </c>
       <c r="AT28" t="n">
-        <v>0.272</v>
+        <v>0.267</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.284</v>
+        <v>1.277</v>
       </c>
       <c r="AV28" t="n">
         <v>0.2</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.058</v>
+        <v>0.059</v>
       </c>
       <c r="AX28" t="n">
         <v>0.146</v>
@@ -4815,118 +4815,118 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C30" t="n">
-        <v>7.844</v>
+        <v>7.853</v>
       </c>
       <c r="D30" t="n">
-        <v>1.656</v>
+        <v>1.647</v>
       </c>
       <c r="E30" t="n">
-        <v>3.375</v>
+        <v>3.294</v>
       </c>
       <c r="F30" t="n">
-        <v>0.969</v>
+        <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>3.594</v>
+        <v>3.588</v>
       </c>
       <c r="H30" t="n">
-        <v>1.625</v>
+        <v>1.559</v>
       </c>
       <c r="I30" t="n">
-        <v>2.219</v>
+        <v>2.147</v>
       </c>
       <c r="J30" t="n">
-        <v>1.812</v>
+        <v>1.794</v>
       </c>
       <c r="K30" t="n">
-        <v>1.688</v>
+        <v>1.706</v>
       </c>
       <c r="L30" t="n">
-        <v>0.531</v>
+        <v>0.529</v>
       </c>
       <c r="M30" t="n">
-        <v>0.875</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="N30" t="n">
-        <v>0.344</v>
+        <v>0.324</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.312</v>
+        <v>1.353</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.312</v>
+        <v>1.353</v>
       </c>
       <c r="R30" t="n">
-        <v>1.75</v>
+        <v>1.765</v>
       </c>
       <c r="S30" t="n">
-        <v>2.312</v>
+        <v>2.294</v>
       </c>
       <c r="T30" t="n">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="U30" t="n">
-        <v>1.062</v>
+        <v>1.088</v>
       </c>
       <c r="V30" t="n">
-        <v>0.344</v>
+        <v>0.382</v>
       </c>
       <c r="W30" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.529</v>
       </c>
       <c r="X30" t="n">
-        <v>0.344</v>
+        <v>0.324</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.375</v>
+        <v>2.324</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.5</v>
+        <v>3.412</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.679</v>
+        <v>0.681</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.594</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.219</v>
+        <v>1.176</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.487</v>
+        <v>0.475</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.312</v>
+        <v>0.324</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.875</v>
+        <v>0.853</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.357</v>
+        <v>0.379</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.094</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.531</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.176</v>
+        <v>0.158</v>
       </c>
       <c r="AK30" t="n">
-        <v>0.875</v>
+        <v>0.912</v>
       </c>
       <c r="AL30" t="n">
-        <v>3.062</v>
+        <v>3.029</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.286</v>
+        <v>0.301</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
@@ -4934,28 +4934,28 @@
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>9.257</v>
+        <v>9.18</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.446</v>
+        <v>0.457</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.494</v>
+        <v>0.502</v>
       </c>
       <c r="AR30" t="n">
-        <v>0.847</v>
+        <v>0.855</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.142</v>
+        <v>0.147</v>
       </c>
       <c r="AT30" t="n">
-        <v>0.233</v>
+        <v>0.226</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.381</v>
+        <v>1.326</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.212</v>
+        <v>0.211</v>
       </c>
       <c r="AW30" t="n">
         <v>0.03</v>
@@ -4974,156 +4974,156 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>7.464</v>
+        <v>7.067</v>
       </c>
       <c r="D31" t="n">
-        <v>1.393</v>
+        <v>1.3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.429</v>
+        <v>2.367</v>
       </c>
       <c r="F31" t="n">
-        <v>0.786</v>
+        <v>0.767</v>
       </c>
       <c r="G31" t="n">
-        <v>2.821</v>
+        <v>2.767</v>
       </c>
       <c r="H31" t="n">
-        <v>2.321</v>
+        <v>2.167</v>
       </c>
       <c r="I31" t="n">
-        <v>2.714</v>
+        <v>2.533</v>
       </c>
       <c r="J31" t="n">
-        <v>2.75</v>
+        <v>2.867</v>
       </c>
       <c r="K31" t="n">
-        <v>1.107</v>
+        <v>1.1</v>
       </c>
       <c r="L31" t="n">
-        <v>0.286</v>
+        <v>0.267</v>
       </c>
       <c r="M31" t="n">
-        <v>0.857</v>
+        <v>0.8</v>
       </c>
       <c r="N31" t="n">
-        <v>0.214</v>
+        <v>0.2</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.107</v>
+        <v>1.033</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.107</v>
+        <v>1.033</v>
       </c>
       <c r="R31" t="n">
-        <v>2.429</v>
+        <v>2.4</v>
       </c>
       <c r="S31" t="n">
-        <v>2.75</v>
+        <v>2.633</v>
       </c>
       <c r="T31" t="n">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="U31" t="n">
-        <v>1</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="V31" t="n">
-        <v>0.5</v>
+        <v>0.467</v>
       </c>
       <c r="W31" t="n">
-        <v>0.143</v>
+        <v>0.233</v>
       </c>
       <c r="X31" t="n">
-        <v>0.143</v>
+        <v>0.167</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.929</v>
+        <v>2.733</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.714</v>
+        <v>3.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.788</v>
+        <v>0.781</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.429</v>
+        <v>0.4</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.607</v>
+        <v>0.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.706</v>
+        <v>0.667</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.357</v>
+        <v>0.333</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.821</v>
+        <v>0.8</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.435</v>
+        <v>0.417</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.179</v>
+        <v>0.167</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.464</v>
+        <v>0.433</v>
       </c>
       <c r="AJ31" t="n">
         <v>0.385</v>
       </c>
       <c r="AK31" t="n">
-        <v>0.607</v>
+        <v>0.6</v>
       </c>
       <c r="AL31" t="n">
-        <v>2.357</v>
+        <v>2.333</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.258</v>
+        <v>0.257</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>7.551</v>
+        <v>7.281</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.49</v>
+        <v>0.477</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.579</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="AR31" t="n">
-        <v>0.988</v>
+        <v>0.971</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.147</v>
+        <v>0.142</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.442</v>
+        <v>0.422</v>
       </c>
       <c r="AU31" t="n">
-        <v>2.484</v>
+        <v>2.774</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.193</v>
+        <v>0.19</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
       <c r="AX31" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.106</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="32">
@@ -5610,156 +5610,156 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>12.875</v>
+        <v>12.706</v>
       </c>
       <c r="D35" t="n">
-        <v>1.781</v>
+        <v>1.765</v>
       </c>
       <c r="E35" t="n">
-        <v>4.406</v>
+        <v>4.324</v>
       </c>
       <c r="F35" t="n">
-        <v>2.312</v>
+        <v>2.265</v>
       </c>
       <c r="G35" t="n">
-        <v>6.094</v>
+        <v>6.059</v>
       </c>
       <c r="H35" t="n">
-        <v>2.375</v>
+        <v>2.382</v>
       </c>
       <c r="I35" t="n">
-        <v>2.656</v>
+        <v>2.676</v>
       </c>
       <c r="J35" t="n">
-        <v>1.281</v>
+        <v>1.206</v>
       </c>
       <c r="K35" t="n">
-        <v>1.031</v>
+        <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>0.219</v>
+        <v>0.235</v>
       </c>
       <c r="M35" t="n">
-        <v>0.656</v>
+        <v>0.647</v>
       </c>
       <c r="N35" t="n">
-        <v>0.594</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1.656</v>
+        <v>1.588</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.656</v>
+        <v>1.588</v>
       </c>
       <c r="R35" t="n">
-        <v>2.094</v>
+        <v>2.118</v>
       </c>
       <c r="S35" t="n">
-        <v>1.688</v>
+        <v>1.706</v>
       </c>
       <c r="T35" t="n">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="U35" t="n">
-        <v>1.719</v>
+        <v>1.882</v>
       </c>
       <c r="V35" t="n">
         <v>1</v>
       </c>
       <c r="W35" t="n">
-        <v>1.438</v>
+        <v>1.382</v>
       </c>
       <c r="X35" t="n">
-        <v>0.719</v>
+        <v>0.706</v>
       </c>
       <c r="Y35" t="n">
-        <v>3.125</v>
+        <v>3.118</v>
       </c>
       <c r="Z35" t="n">
-        <v>4</v>
+        <v>3.971</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.781</v>
+        <v>0.785</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.312</v>
+        <v>0.324</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.031</v>
+        <v>1.029</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.303</v>
+        <v>0.314</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.719</v>
+        <v>0.706</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.031</v>
+        <v>2</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.354</v>
+        <v>0.353</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.438</v>
+        <v>0.412</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.156</v>
+        <v>1.147</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.378</v>
+        <v>0.359</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.875</v>
+        <v>1.853</v>
       </c>
       <c r="AL35" t="n">
-        <v>4.938</v>
+        <v>4.912</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.38</v>
+        <v>0.377</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>22:53</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>13.325</v>
+        <v>13.148</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.5</v>
+        <v>0.497</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.552</v>
+        <v>0.55</v>
       </c>
       <c r="AR35" t="n">
         <v>0.966</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.124</v>
+        <v>0.121</v>
       </c>
       <c r="AT35" t="n">
-        <v>0.226</v>
+        <v>0.229</v>
       </c>
       <c r="AU35" t="n">
-        <v>0.774</v>
+        <v>0.759</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.269</v>
+        <v>0.267</v>
       </c>
       <c r="AW35" t="n">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.051</v>
+        <v>0.049</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.053</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="36">
@@ -6087,156 +6087,156 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C38" t="n">
-        <v>8.561999999999999</v>
+        <v>8.206</v>
       </c>
       <c r="D38" t="n">
-        <v>2.031</v>
+        <v>1.912</v>
       </c>
       <c r="E38" t="n">
-        <v>3.156</v>
+        <v>3.029</v>
       </c>
       <c r="F38" t="n">
-        <v>0.906</v>
+        <v>0.853</v>
       </c>
       <c r="G38" t="n">
-        <v>2.062</v>
+        <v>2</v>
       </c>
       <c r="H38" t="n">
-        <v>1.781</v>
+        <v>1.824</v>
       </c>
       <c r="I38" t="n">
-        <v>2.438</v>
+        <v>2.471</v>
       </c>
       <c r="J38" t="n">
-        <v>0.875</v>
+        <v>0.853</v>
       </c>
       <c r="K38" t="n">
-        <v>2.531</v>
+        <v>2.5</v>
       </c>
       <c r="L38" t="n">
-        <v>0.844</v>
+        <v>0.853</v>
       </c>
       <c r="M38" t="n">
-        <v>0.719</v>
+        <v>0.676</v>
       </c>
       <c r="N38" t="n">
-        <v>0.875</v>
+        <v>0.824</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="R38" t="n">
-        <v>3.375</v>
+        <v>3.353</v>
       </c>
       <c r="S38" t="n">
-        <v>2.5</v>
+        <v>2.471</v>
       </c>
       <c r="T38" t="n">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="U38" t="n">
-        <v>1.5</v>
+        <v>1.471</v>
       </c>
       <c r="V38" t="n">
-        <v>1.125</v>
+        <v>1.118</v>
       </c>
       <c r="W38" t="n">
-        <v>0.469</v>
+        <v>0.441</v>
       </c>
       <c r="X38" t="n">
-        <v>0.25</v>
+        <v>0.235</v>
       </c>
       <c r="Y38" t="n">
-        <v>3.625</v>
+        <v>3.559</v>
       </c>
       <c r="Z38" t="n">
-        <v>4.844</v>
+        <v>4.735</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.748</v>
+        <v>0.752</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.094</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AC38" t="n">
-        <v>0.344</v>
+        <v>0.382</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.273</v>
+        <v>0.231</v>
       </c>
       <c r="AE38" t="n">
-        <v>0.094</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.406</v>
+        <v>0.382</v>
       </c>
       <c r="AG38" t="n">
         <v>0.231</v>
       </c>
       <c r="AH38" t="n">
-        <v>0.219</v>
+        <v>0.206</v>
       </c>
       <c r="AI38" t="n">
-        <v>0.531</v>
+        <v>0.529</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0.412</v>
+        <v>0.389</v>
       </c>
       <c r="AK38" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.647</v>
       </c>
       <c r="AL38" t="n">
-        <v>1.531</v>
+        <v>1.471</v>
       </c>
       <c r="AM38" t="n">
-        <v>0.449</v>
+        <v>0.44</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AO38" t="n">
-        <v>7.229</v>
+        <v>7.058</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.65</v>
+        <v>0.635</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.681</v>
+        <v>0.671</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.185</v>
+        <v>1.163</v>
       </c>
       <c r="AS38" t="n">
-        <v>0.13</v>
+        <v>0.133</v>
       </c>
       <c r="AT38" t="n">
-        <v>0.341</v>
+        <v>0.363</v>
       </c>
       <c r="AU38" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.906</v>
       </c>
       <c r="AV38" t="n">
-        <v>0.18</v>
+        <v>0.178</v>
       </c>
       <c r="AW38" t="n">
-        <v>0.052</v>
+        <v>0.053</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.155</v>
+        <v>0.154</v>
       </c>
       <c r="AY38" t="n">
-        <v>0.035</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="39">
@@ -6246,156 +6246,156 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C39" t="n">
-        <v>12.633</v>
+        <v>12.719</v>
       </c>
       <c r="D39" t="n">
-        <v>2.4</v>
+        <v>2.312</v>
       </c>
       <c r="E39" t="n">
-        <v>5.033</v>
+        <v>4.906</v>
       </c>
       <c r="F39" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="G39" t="n">
-        <v>5.467</v>
+        <v>5.406</v>
       </c>
       <c r="H39" t="n">
-        <v>2.733</v>
+        <v>2.844</v>
       </c>
       <c r="I39" t="n">
-        <v>3.333</v>
+        <v>3.469</v>
       </c>
       <c r="J39" t="n">
-        <v>2.667</v>
+        <v>2.688</v>
       </c>
       <c r="K39" t="n">
-        <v>2.433</v>
+        <v>2.375</v>
       </c>
       <c r="L39" t="n">
-        <v>0.6</v>
+        <v>0.594</v>
       </c>
       <c r="M39" t="n">
-        <v>0.967</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="N39" t="n">
-        <v>0.4</v>
+        <v>0.406</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2.4</v>
+        <v>2.469</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.4</v>
+        <v>2.469</v>
       </c>
       <c r="R39" t="n">
-        <v>2.233</v>
+        <v>2.25</v>
       </c>
       <c r="S39" t="n">
-        <v>2.533</v>
+        <v>2.625</v>
       </c>
       <c r="T39" t="n">
-        <v>318</v>
+        <v>344</v>
       </c>
       <c r="U39" t="n">
-        <v>1.633</v>
+        <v>1.656</v>
       </c>
       <c r="V39" t="n">
-        <v>1.267</v>
+        <v>1.281</v>
       </c>
       <c r="W39" t="n">
-        <v>0.6</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="X39" t="n">
-        <v>0.267</v>
+        <v>0.25</v>
       </c>
       <c r="Y39" t="n">
-        <v>4.067</v>
+        <v>4.156</v>
       </c>
       <c r="Z39" t="n">
-        <v>5.5</v>
+        <v>5.625</v>
       </c>
       <c r="AA39" t="n">
         <v>0.739</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.6</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.6</v>
+        <v>1.562</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.375</v>
+        <v>0.36</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.467</v>
+        <v>0.438</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.267</v>
+        <v>1.188</v>
       </c>
       <c r="AG39" t="n">
         <v>0.368</v>
       </c>
       <c r="AH39" t="n">
-        <v>0.267</v>
+        <v>0.344</v>
       </c>
       <c r="AI39" t="n">
-        <v>0.733</v>
+        <v>0.781</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.364</v>
+        <v>0.44</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.433</v>
+        <v>1.406</v>
       </c>
       <c r="AL39" t="n">
-        <v>4.733</v>
+        <v>4.625</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.303</v>
+        <v>0.304</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>23:55</t>
+          <t>24:00</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>14.367</v>
+        <v>14.307</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.471</v>
+        <v>0.479</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.528</v>
+        <v>0.537</v>
       </c>
       <c r="AR39" t="n">
-        <v>0.879</v>
+        <v>0.889</v>
       </c>
       <c r="AS39" t="n">
-        <v>0.167</v>
+        <v>0.173</v>
       </c>
       <c r="AT39" t="n">
-        <v>0.26</v>
+        <v>0.276</v>
       </c>
       <c r="AU39" t="n">
-        <v>1.111</v>
+        <v>1.089</v>
       </c>
       <c r="AV39" t="n">
-        <v>0.278</v>
+        <v>0.277</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.029</v>
+        <v>0.028</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.116</v>
+        <v>0.112</v>
       </c>
       <c r="AY39" t="n">
-        <v>0.111</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="40">
@@ -6564,97 +6564,97 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C41" t="n">
-        <v>3.867</v>
+        <v>3.75</v>
       </c>
       <c r="D41" t="n">
-        <v>1.333</v>
+        <v>1.312</v>
       </c>
       <c r="E41" t="n">
-        <v>2.1</v>
+        <v>2.031</v>
       </c>
       <c r="F41" t="n">
-        <v>0.067</v>
+        <v>0.062</v>
       </c>
       <c r="G41" t="n">
-        <v>0.3</v>
+        <v>0.281</v>
       </c>
       <c r="H41" t="n">
-        <v>1</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>1.4</v>
+        <v>1.438</v>
       </c>
       <c r="J41" t="n">
-        <v>0.333</v>
+        <v>0.312</v>
       </c>
       <c r="K41" t="n">
-        <v>2.2</v>
+        <v>2.125</v>
       </c>
       <c r="L41" t="n">
-        <v>1.2</v>
+        <v>1.125</v>
       </c>
       <c r="M41" t="n">
-        <v>0.333</v>
+        <v>0.344</v>
       </c>
       <c r="N41" t="n">
-        <v>0.433</v>
+        <v>0.438</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>0.9</v>
+        <v>0.875</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.9</v>
+        <v>0.875</v>
       </c>
       <c r="R41" t="n">
-        <v>1.933</v>
+        <v>1.906</v>
       </c>
       <c r="S41" t="n">
-        <v>1.533</v>
+        <v>1.5</v>
       </c>
       <c r="T41" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="U41" t="n">
-        <v>0.4</v>
+        <v>0.375</v>
       </c>
       <c r="V41" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.531</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>0.031</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.067</v>
+        <v>2</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.9</v>
+        <v>2.906</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.713</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.2</v>
+        <v>0.188</v>
       </c>
       <c r="AC41" t="n">
-        <v>0.4</v>
+        <v>0.375</v>
       </c>
       <c r="AD41" t="n">
         <v>0.5</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.067</v>
+        <v>0.062</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.2</v>
+        <v>0.188</v>
       </c>
       <c r="AG41" t="n">
         <v>0.333</v>
@@ -6663,54 +6663,54 @@
         <v>0</v>
       </c>
       <c r="AI41" t="n">
-        <v>0.033</v>
+        <v>0.031</v>
       </c>
       <c r="AJ41" t="n">
         <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>0.067</v>
+        <v>0.062</v>
       </c>
       <c r="AL41" t="n">
-        <v>0.267</v>
+        <v>0.25</v>
       </c>
       <c r="AM41" t="n">
         <v>0.25</v>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AO41" t="n">
-        <v>3.916</v>
+        <v>3.82</v>
       </c>
       <c r="AP41" t="n">
-        <v>0.597</v>
+        <v>0.608</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.641</v>
+        <v>0.637</v>
       </c>
       <c r="AR41" t="n">
-        <v>0.987</v>
+        <v>0.982</v>
       </c>
       <c r="AS41" t="n">
-        <v>0.23</v>
+        <v>0.229</v>
       </c>
       <c r="AT41" t="n">
-        <v>0.417</v>
+        <v>0.405</v>
       </c>
       <c r="AU41" t="n">
-        <v>0.37</v>
+        <v>0.357</v>
       </c>
       <c r="AV41" t="n">
-        <v>0.145</v>
+        <v>0.143</v>
       </c>
       <c r="AW41" t="n">
-        <v>0.109</v>
+        <v>0.105</v>
       </c>
       <c r="AX41" t="n">
-        <v>0.2</v>
+        <v>0.194</v>
       </c>
       <c r="AY41" t="n">
         <v>0.012</v>
@@ -6723,153 +6723,153 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C42" t="n">
-        <v>7.188</v>
+        <v>7.265</v>
       </c>
       <c r="D42" t="n">
-        <v>1.406</v>
+        <v>1.382</v>
       </c>
       <c r="E42" t="n">
-        <v>2.438</v>
+        <v>2.382</v>
       </c>
       <c r="F42" t="n">
-        <v>1.125</v>
+        <v>1.147</v>
       </c>
       <c r="G42" t="n">
-        <v>3.031</v>
+        <v>3.147</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>1.059</v>
       </c>
       <c r="I42" t="n">
-        <v>1.25</v>
+        <v>1.294</v>
       </c>
       <c r="J42" t="n">
-        <v>0.875</v>
+        <v>0.853</v>
       </c>
       <c r="K42" t="n">
-        <v>2.188</v>
+        <v>2.294</v>
       </c>
       <c r="L42" t="n">
-        <v>0.844</v>
+        <v>0.824</v>
       </c>
       <c r="M42" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="N42" t="n">
-        <v>0.281</v>
+        <v>0.265</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>0.906</v>
+        <v>0.912</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.906</v>
+        <v>0.912</v>
       </c>
       <c r="R42" t="n">
-        <v>1.969</v>
+        <v>1.971</v>
       </c>
       <c r="S42" t="n">
-        <v>1.062</v>
+        <v>1.059</v>
       </c>
       <c r="T42" t="n">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="U42" t="n">
-        <v>1.344</v>
+        <v>1.265</v>
       </c>
       <c r="V42" t="n">
-        <v>0.719</v>
+        <v>0.676</v>
       </c>
       <c r="W42" t="n">
-        <v>0.375</v>
+        <v>0.353</v>
       </c>
       <c r="X42" t="n">
-        <v>0.25</v>
+        <v>0.235</v>
       </c>
       <c r="Y42" t="n">
-        <v>2.094</v>
+        <v>2.118</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.688</v>
+        <v>2.706</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.779</v>
+        <v>0.783</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.125</v>
+        <v>0.118</v>
       </c>
       <c r="AC42" t="n">
-        <v>0.531</v>
+        <v>0.5</v>
       </c>
       <c r="AD42" t="n">
         <v>0.235</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.188</v>
+        <v>0.206</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.469</v>
+        <v>0.471</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.4</v>
+        <v>0.438</v>
       </c>
       <c r="AH42" t="n">
         <v>0.5</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.062</v>
+        <v>1.118</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.471</v>
+        <v>0.447</v>
       </c>
       <c r="AK42" t="n">
-        <v>0.625</v>
+        <v>0.647</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.969</v>
+        <v>2.029</v>
       </c>
       <c r="AM42" t="n">
-        <v>0.317</v>
+        <v>0.319</v>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>21:07</t>
+          <t>21:16</t>
         </is>
       </c>
       <c r="AO42" t="n">
-        <v>6.925</v>
+        <v>7.011</v>
       </c>
       <c r="AP42" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.597</v>
+        <v>0.596</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.038</v>
+        <v>1.036</v>
       </c>
       <c r="AS42" t="n">
-        <v>0.131</v>
+        <v>0.13</v>
       </c>
       <c r="AT42" t="n">
-        <v>0.183</v>
+        <v>0.191</v>
       </c>
       <c r="AU42" t="n">
-        <v>0.966</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="AV42" t="n">
-        <v>0.152</v>
+        <v>0.153</v>
       </c>
       <c r="AW42" t="n">
         <v>0.045</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.118</v>
+        <v>0.122</v>
       </c>
       <c r="AY42" t="n">
         <v>0.034</v>
@@ -6882,156 +6882,156 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C43" t="n">
-        <v>10.656</v>
+        <v>11.059</v>
       </c>
       <c r="D43" t="n">
-        <v>2.031</v>
+        <v>2.088</v>
       </c>
       <c r="E43" t="n">
-        <v>4.625</v>
+        <v>4.647</v>
       </c>
       <c r="F43" t="n">
-        <v>0.969</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="G43" t="n">
-        <v>1.969</v>
+        <v>2.029</v>
       </c>
       <c r="H43" t="n">
-        <v>3.688</v>
+        <v>4.059</v>
       </c>
       <c r="I43" t="n">
-        <v>4.688</v>
+        <v>5.118</v>
       </c>
       <c r="J43" t="n">
-        <v>4.125</v>
+        <v>4.118</v>
       </c>
       <c r="K43" t="n">
-        <v>3.5</v>
+        <v>3.471</v>
       </c>
       <c r="L43" t="n">
-        <v>0.656</v>
+        <v>0.676</v>
       </c>
       <c r="M43" t="n">
-        <v>1.125</v>
+        <v>1.088</v>
       </c>
       <c r="N43" t="n">
-        <v>0.469</v>
+        <v>0.441</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>1.781</v>
+        <v>1.765</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.781</v>
+        <v>1.765</v>
       </c>
       <c r="R43" t="n">
-        <v>1.469</v>
+        <v>1.5</v>
       </c>
       <c r="S43" t="n">
-        <v>4.5</v>
+        <v>4.647</v>
       </c>
       <c r="T43" t="n">
-        <v>550</v>
+        <v>596</v>
       </c>
       <c r="U43" t="n">
-        <v>1.75</v>
+        <v>1.765</v>
       </c>
       <c r="V43" t="n">
-        <v>0.531</v>
+        <v>0.5</v>
       </c>
       <c r="W43" t="n">
-        <v>0.438</v>
+        <v>0.5</v>
       </c>
       <c r="X43" t="n">
-        <v>0.312</v>
+        <v>0.382</v>
       </c>
       <c r="Y43" t="n">
-        <v>4.875</v>
+        <v>5.324</v>
       </c>
       <c r="Z43" t="n">
-        <v>6.969</v>
+        <v>7.412</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.7</v>
+        <v>0.718</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.375</v>
+        <v>0.382</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.188</v>
+        <v>1.206</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.316</v>
+        <v>0.317</v>
       </c>
       <c r="AE43" t="n">
-        <v>0.469</v>
+        <v>0.441</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.156</v>
+        <v>1.147</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.405</v>
+        <v>0.385</v>
       </c>
       <c r="AH43" t="n">
-        <v>0.188</v>
+        <v>0.176</v>
       </c>
       <c r="AI43" t="n">
-        <v>0.25</v>
+        <v>0.265</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.75</v>
+        <v>0.667</v>
       </c>
       <c r="AK43" t="n">
-        <v>0.781</v>
+        <v>0.765</v>
       </c>
       <c r="AL43" t="n">
-        <v>1.719</v>
+        <v>1.765</v>
       </c>
       <c r="AM43" t="n">
-        <v>0.455</v>
+        <v>0.433</v>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>24:03</t>
+          <t>24:10</t>
         </is>
       </c>
       <c r="AO43" t="n">
-        <v>10.438</v>
+        <v>10.693</v>
       </c>
       <c r="AP43" t="n">
-        <v>0.528</v>
+        <v>0.524</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.616</v>
+        <v>0.619</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.021</v>
+        <v>1.034</v>
       </c>
       <c r="AS43" t="n">
-        <v>0.171</v>
+        <v>0.165</v>
       </c>
       <c r="AT43" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.608</v>
       </c>
       <c r="AU43" t="n">
-        <v>2.316</v>
+        <v>2.333</v>
       </c>
       <c r="AV43" t="n">
-        <v>0.201</v>
+        <v>0.205</v>
       </c>
       <c r="AW43" t="n">
-        <v>0.031</v>
+        <v>0.032</v>
       </c>
       <c r="AX43" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="AY43" t="n">
         <v>0.165</v>
-      </c>
-      <c r="AY43" t="n">
-        <v>0.164</v>
       </c>
     </row>
     <row r="44">
@@ -7041,67 +7041,67 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C44" t="n">
-        <v>1.526</v>
+        <v>1.381</v>
       </c>
       <c r="D44" t="n">
-        <v>0.632</v>
+        <v>0.571</v>
       </c>
       <c r="E44" t="n">
-        <v>1.053</v>
+        <v>0.952</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0.105</v>
+        <v>0.095</v>
       </c>
       <c r="H44" t="n">
-        <v>0.263</v>
+        <v>0.238</v>
       </c>
       <c r="I44" t="n">
-        <v>0.579</v>
+        <v>0.524</v>
       </c>
       <c r="J44" t="n">
-        <v>0.105</v>
+        <v>0.095</v>
       </c>
       <c r="K44" t="n">
-        <v>0.895</v>
+        <v>0.857</v>
       </c>
       <c r="L44" t="n">
-        <v>0.421</v>
+        <v>0.381</v>
       </c>
       <c r="M44" t="n">
-        <v>0.105</v>
+        <v>0.095</v>
       </c>
       <c r="N44" t="n">
-        <v>0.158</v>
+        <v>0.143</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>0.105</v>
+        <v>0.095</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.105</v>
+        <v>0.095</v>
       </c>
       <c r="R44" t="n">
-        <v>0.368</v>
+        <v>0.333</v>
       </c>
       <c r="S44" t="n">
-        <v>0.421</v>
+        <v>0.381</v>
       </c>
       <c r="T44" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="U44" t="n">
-        <v>0.263</v>
+        <v>0.238</v>
       </c>
       <c r="V44" t="n">
-        <v>0.737</v>
+        <v>0.667</v>
       </c>
       <c r="W44" t="n">
         <v>0</v>
@@ -7110,19 +7110,19 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.842</v>
+        <v>0.762</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.368</v>
+        <v>1.238</v>
       </c>
       <c r="AA44" t="n">
         <v>0.615</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.053</v>
+        <v>0.048</v>
       </c>
       <c r="AC44" t="n">
-        <v>0.158</v>
+        <v>0.143</v>
       </c>
       <c r="AD44" t="n">
         <v>0.333</v>
@@ -7131,7 +7131,7 @@
         <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.105</v>
+        <v>0.095</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -7149,18 +7149,18 @@
         <v>0</v>
       </c>
       <c r="AL44" t="n">
-        <v>0.105</v>
+        <v>0.095</v>
       </c>
       <c r="AM44" t="n">
         <v>0</v>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>05:43</t>
+          <t>05:23</t>
         </is>
       </c>
       <c r="AO44" t="n">
-        <v>1.518</v>
+        <v>1.373</v>
       </c>
       <c r="AP44" t="n">
         <v>0.545</v>
@@ -7181,16 +7181,16 @@
         <v>1</v>
       </c>
       <c r="AV44" t="n">
-        <v>0.123</v>
+        <v>0.118</v>
       </c>
       <c r="AW44" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.081</v>
       </c>
       <c r="AX44" t="n">
-        <v>0.178</v>
+        <v>0.18</v>
       </c>
       <c r="AY44" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="45">
@@ -7200,156 +7200,156 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C45" t="n">
-        <v>2.719</v>
+        <v>3.088</v>
       </c>
       <c r="D45" t="n">
-        <v>0.5</v>
+        <v>0.529</v>
       </c>
       <c r="E45" t="n">
-        <v>0.906</v>
+        <v>0.912</v>
       </c>
       <c r="F45" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.647</v>
       </c>
       <c r="G45" t="n">
-        <v>1.656</v>
+        <v>1.794</v>
       </c>
       <c r="H45" t="n">
-        <v>0.031</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>0.062</v>
+        <v>0.118</v>
       </c>
       <c r="J45" t="n">
-        <v>0.344</v>
+        <v>0.412</v>
       </c>
       <c r="K45" t="n">
-        <v>0.438</v>
+        <v>0.441</v>
       </c>
       <c r="L45" t="n">
-        <v>0.312</v>
+        <v>0.353</v>
       </c>
       <c r="M45" t="n">
-        <v>0.156</v>
+        <v>0.235</v>
       </c>
       <c r="N45" t="n">
-        <v>0.188</v>
+        <v>0.176</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>0.281</v>
+        <v>0.382</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.281</v>
+        <v>0.382</v>
       </c>
       <c r="R45" t="n">
-        <v>1.344</v>
+        <v>1.294</v>
       </c>
       <c r="S45" t="n">
-        <v>0.188</v>
+        <v>0.235</v>
       </c>
       <c r="T45" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="U45" t="n">
-        <v>0.594</v>
+        <v>0.618</v>
       </c>
       <c r="V45" t="n">
-        <v>0.281</v>
+        <v>0.265</v>
       </c>
       <c r="W45" t="n">
-        <v>0.188</v>
+        <v>0.265</v>
       </c>
       <c r="X45" t="n">
-        <v>0.094</v>
+        <v>0.118</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.25</v>
+        <v>0.353</v>
       </c>
       <c r="Z45" t="n">
-        <v>0.469</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.533</v>
+        <v>0.632</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.219</v>
+        <v>0.206</v>
       </c>
       <c r="AC45" t="n">
-        <v>0.344</v>
+        <v>0.324</v>
       </c>
       <c r="AD45" t="n">
         <v>0.636</v>
       </c>
       <c r="AE45" t="n">
-        <v>0.062</v>
+        <v>0.059</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.156</v>
+        <v>0.147</v>
       </c>
       <c r="AG45" t="n">
         <v>0.4</v>
       </c>
       <c r="AH45" t="n">
-        <v>0.312</v>
+        <v>0.324</v>
       </c>
       <c r="AI45" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.735</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0.455</v>
+        <v>0.44</v>
       </c>
       <c r="AK45" t="n">
-        <v>0.25</v>
+        <v>0.324</v>
       </c>
       <c r="AL45" t="n">
-        <v>0.969</v>
+        <v>1.059</v>
       </c>
       <c r="AM45" t="n">
-        <v>0.258</v>
+        <v>0.306</v>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AO45" t="n">
-        <v>2.871</v>
+        <v>3.14</v>
       </c>
       <c r="AP45" t="n">
-        <v>0.524</v>
+        <v>0.554</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.525</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR45" t="n">
-        <v>0.947</v>
+        <v>0.984</v>
       </c>
       <c r="AS45" t="n">
-        <v>0.098</v>
+        <v>0.122</v>
       </c>
       <c r="AT45" t="n">
-        <v>0.012</v>
+        <v>0.033</v>
       </c>
       <c r="AU45" t="n">
-        <v>1.222</v>
+        <v>1.077</v>
       </c>
       <c r="AV45" t="n">
-        <v>0.165</v>
+        <v>0.175</v>
       </c>
       <c r="AW45" t="n">
-        <v>0.044</v>
+        <v>0.049</v>
       </c>
       <c r="AX45" t="n">
-        <v>0.062</v>
+        <v>0.06</v>
       </c>
       <c r="AY45" t="n">
-        <v>0.013</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="46">
@@ -7359,16 +7359,16 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C46" t="n">
-        <v>9.875</v>
+        <v>10.088</v>
       </c>
       <c r="D46" t="n">
-        <v>3.625</v>
+        <v>3.706</v>
       </c>
       <c r="E46" t="n">
-        <v>5.281</v>
+        <v>5.294</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -7377,79 +7377,79 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>2.625</v>
+        <v>2.676</v>
       </c>
       <c r="I46" t="n">
-        <v>4.688</v>
+        <v>4.676</v>
       </c>
       <c r="J46" t="n">
-        <v>1.719</v>
+        <v>1.706</v>
       </c>
       <c r="K46" t="n">
-        <v>4.375</v>
+        <v>4.5</v>
       </c>
       <c r="L46" t="n">
-        <v>2.188</v>
+        <v>2.176</v>
       </c>
       <c r="M46" t="n">
-        <v>0.531</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="N46" t="n">
-        <v>1.719</v>
+        <v>1.647</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>1.531</v>
+        <v>1.529</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.531</v>
+        <v>1.529</v>
       </c>
       <c r="R46" t="n">
-        <v>2.438</v>
+        <v>2.382</v>
       </c>
       <c r="S46" t="n">
-        <v>3.75</v>
+        <v>3.853</v>
       </c>
       <c r="T46" t="n">
-        <v>527</v>
+        <v>579</v>
       </c>
       <c r="U46" t="n">
-        <v>0.625</v>
+        <v>0.706</v>
       </c>
       <c r="V46" t="n">
-        <v>1.812</v>
+        <v>1.824</v>
       </c>
       <c r="W46" t="n">
-        <v>0.25</v>
+        <v>0.265</v>
       </c>
       <c r="X46" t="n">
-        <v>0.156</v>
+        <v>0.176</v>
       </c>
       <c r="Y46" t="n">
-        <v>5.781</v>
+        <v>5.912</v>
       </c>
       <c r="Z46" t="n">
-        <v>8.781000000000001</v>
+        <v>8.794</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.658</v>
+        <v>0.672</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.469</v>
+        <v>0.471</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.094</v>
+        <v>1.088</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.429</v>
+        <v>0.432</v>
       </c>
       <c r="AE46" t="n">
         <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.094</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -7474,38 +7474,38 @@
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>23:36</t>
         </is>
       </c>
       <c r="AO46" t="n">
-        <v>8.875</v>
+        <v>8.881</v>
       </c>
       <c r="AP46" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AQ46" t="n">
         <v>0.6860000000000001</v>
       </c>
-      <c r="AQ46" t="n">
-        <v>0.672</v>
-      </c>
       <c r="AR46" t="n">
-        <v>1.113</v>
+        <v>1.136</v>
       </c>
       <c r="AS46" t="n">
-        <v>0.173</v>
+        <v>0.172</v>
       </c>
       <c r="AT46" t="n">
-        <v>0.497</v>
+        <v>0.506</v>
       </c>
       <c r="AU46" t="n">
-        <v>1.122</v>
+        <v>1.115</v>
       </c>
       <c r="AV46" t="n">
-        <v>0.176</v>
+        <v>0.175</v>
       </c>
       <c r="AW46" t="n">
-        <v>0.107</v>
+        <v>0.106</v>
       </c>
       <c r="AX46" t="n">
-        <v>0.213</v>
+        <v>0.215</v>
       </c>
       <c r="AY46" t="n">
         <v>0.07000000000000001</v>
@@ -7518,126 +7518,126 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C47" t="n">
-        <v>2.68</v>
+        <v>2.481</v>
       </c>
       <c r="D47" t="n">
-        <v>0.8</v>
+        <v>0.741</v>
       </c>
       <c r="E47" t="n">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="F47" t="n">
-        <v>0.24</v>
+        <v>0.222</v>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>0.926</v>
       </c>
       <c r="H47" t="n">
-        <v>0.36</v>
+        <v>0.333</v>
       </c>
       <c r="I47" t="n">
-        <v>0.52</v>
+        <v>0.481</v>
       </c>
       <c r="J47" t="n">
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
       <c r="K47" t="n">
-        <v>2</v>
+        <v>1.889</v>
       </c>
       <c r="L47" t="n">
-        <v>0.84</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="M47" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="N47" t="n">
-        <v>0.12</v>
+        <v>0.111</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>0.64</v>
+        <v>0.593</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.64</v>
+        <v>0.593</v>
       </c>
       <c r="R47" t="n">
-        <v>2.32</v>
+        <v>2.222</v>
       </c>
       <c r="S47" t="n">
-        <v>0.72</v>
+        <v>0.667</v>
       </c>
       <c r="T47" t="n">
         <v>65</v>
       </c>
       <c r="U47" t="n">
-        <v>0.28</v>
+        <v>0.259</v>
       </c>
       <c r="V47" t="n">
-        <v>0.16</v>
+        <v>0.148</v>
       </c>
       <c r="W47" t="n">
-        <v>0.04</v>
+        <v>0.037</v>
       </c>
       <c r="X47" t="n">
-        <v>0.04</v>
+        <v>0.037</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.72</v>
+        <v>0.667</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.32</v>
+        <v>1.222</v>
       </c>
       <c r="AA47" t="n">
         <v>0.545</v>
       </c>
       <c r="AB47" t="n">
-        <v>0.28</v>
+        <v>0.259</v>
       </c>
       <c r="AC47" t="n">
-        <v>0.48</v>
+        <v>0.444</v>
       </c>
       <c r="AD47" t="n">
         <v>0.583</v>
       </c>
       <c r="AE47" t="n">
-        <v>0.16</v>
+        <v>0.148</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.48</v>
+        <v>0.444</v>
       </c>
       <c r="AG47" t="n">
         <v>0.333</v>
       </c>
       <c r="AH47" t="n">
-        <v>0.04</v>
+        <v>0.037</v>
       </c>
       <c r="AI47" t="n">
-        <v>0.08</v>
+        <v>0.074</v>
       </c>
       <c r="AJ47" t="n">
         <v>0.5</v>
       </c>
       <c r="AK47" t="n">
-        <v>0.2</v>
+        <v>0.185</v>
       </c>
       <c r="AL47" t="n">
-        <v>0.92</v>
+        <v>0.852</v>
       </c>
       <c r="AM47" t="n">
         <v>0.217</v>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AO47" t="n">
-        <v>3.629</v>
+        <v>3.36</v>
       </c>
       <c r="AP47" t="n">
         <v>0.42</v>
@@ -7661,13 +7661,13 @@
         <v>0.118</v>
       </c>
       <c r="AW47" t="n">
-        <v>0.067</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AX47" t="n">
-        <v>0.16</v>
+        <v>0.161</v>
       </c>
       <c r="AY47" t="n">
-        <v>0.025</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="48">
@@ -7677,7 +7677,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
@@ -7704,10 +7704,10 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>2.188</v>
+        <v>2.147</v>
       </c>
       <c r="L48" t="n">
-        <v>1.125</v>
+        <v>1.059</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -7719,13 +7719,13 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>1.031</v>
+        <v>1.029</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>0.062</v>
+        <v>0.059</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -7836,144 +7836,144 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C49" t="n">
-        <v>84.71899999999999</v>
+        <v>84.824</v>
       </c>
       <c r="D49" t="n">
-        <v>18.75</v>
+        <v>18.529</v>
       </c>
       <c r="E49" t="n">
-        <v>35</v>
+        <v>34.382</v>
       </c>
       <c r="F49" t="n">
-        <v>9.375</v>
+        <v>9.412000000000001</v>
       </c>
       <c r="G49" t="n">
-        <v>27.125</v>
+        <v>27.206</v>
       </c>
       <c r="H49" t="n">
-        <v>19.094</v>
+        <v>19.529</v>
       </c>
       <c r="I49" t="n">
-        <v>25.562</v>
+        <v>26.059</v>
       </c>
       <c r="J49" t="n">
-        <v>16.844</v>
+        <v>16.853</v>
       </c>
       <c r="K49" t="n">
-        <v>25.344</v>
+        <v>25.294</v>
       </c>
       <c r="L49" t="n">
-        <v>9.561999999999999</v>
+        <v>9.441000000000001</v>
       </c>
       <c r="M49" t="n">
-        <v>6.969</v>
+        <v>6.971</v>
       </c>
       <c r="N49" t="n">
-        <v>5.625</v>
+        <v>5.382</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>14.062</v>
+        <v>14.088</v>
       </c>
       <c r="Q49" t="n">
-        <v>13.031</v>
+        <v>13.059</v>
       </c>
       <c r="R49" t="n">
-        <v>22.625</v>
+        <v>22.5</v>
       </c>
       <c r="S49" t="n">
-        <v>23.031</v>
+        <v>23.235</v>
       </c>
       <c r="T49" t="n">
-        <v>3038</v>
+        <v>3238</v>
       </c>
       <c r="U49" t="n">
-        <v>11.75</v>
+        <v>11.882</v>
       </c>
       <c r="V49" t="n">
-        <v>8.531000000000001</v>
+        <v>8.412000000000001</v>
       </c>
       <c r="W49" t="n">
-        <v>4.438</v>
+        <v>4.559</v>
       </c>
       <c r="X49" t="n">
-        <v>2.531</v>
+        <v>2.618</v>
       </c>
       <c r="Y49" t="n">
-        <v>31.5</v>
+        <v>31.912</v>
       </c>
       <c r="Z49" t="n">
-        <v>44.219</v>
+        <v>44.441</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.712</v>
+        <v>0.718</v>
       </c>
       <c r="AB49" t="n">
-        <v>3.562</v>
+        <v>3.441</v>
       </c>
       <c r="AC49" t="n">
-        <v>8.625</v>
+        <v>8.5</v>
       </c>
       <c r="AD49" t="n">
-        <v>0.413</v>
+        <v>0.405</v>
       </c>
       <c r="AE49" t="n">
-        <v>2.781</v>
+        <v>2.706</v>
       </c>
       <c r="AF49" t="n">
-        <v>7.719</v>
+        <v>7.5</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.36</v>
+        <v>0.361</v>
       </c>
       <c r="AH49" t="n">
-        <v>2.188</v>
+        <v>2.206</v>
       </c>
       <c r="AI49" t="n">
-        <v>5.406</v>
+        <v>5.559</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0.405</v>
+        <v>0.397</v>
       </c>
       <c r="AK49" t="n">
-        <v>7.188</v>
+        <v>7.206</v>
       </c>
       <c r="AL49" t="n">
-        <v>21.719</v>
+        <v>21.647</v>
       </c>
       <c r="AM49" t="n">
-        <v>0.331</v>
+        <v>0.333</v>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>202:20</t>
+          <t>202:12</t>
         </is>
       </c>
       <c r="AO49" t="n">
-        <v>87.435</v>
+        <v>87.142</v>
       </c>
       <c r="AP49" t="n">
-        <v>0.528</v>
+        <v>0.53</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0.577</v>
+        <v>0.581</v>
       </c>
       <c r="AR49" t="n">
-        <v>0.969</v>
+        <v>0.973</v>
       </c>
       <c r="AS49" t="n">
-        <v>0.161</v>
+        <v>0.162</v>
       </c>
       <c r="AT49" t="n">
-        <v>0.307</v>
+        <v>0.317</v>
       </c>
       <c r="AU49" t="n">
-        <v>1.198</v>
+        <v>1.196</v>
       </c>
       <c r="AV49" t="n">
         <v>0.2</v>
@@ -7982,7 +7982,7 @@
         <v>0.054</v>
       </c>
       <c r="AX49" t="n">
-        <v>0.142</v>
+        <v>0.141</v>
       </c>
       <c r="AY49" t="n">
         <v>0</v>
@@ -7995,153 +7995,153 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C50" t="n">
-        <v>86.312</v>
+        <v>86</v>
       </c>
       <c r="D50" t="n">
-        <v>20.438</v>
+        <v>20.382</v>
       </c>
       <c r="E50" t="n">
-        <v>37.469</v>
+        <v>37.529</v>
       </c>
       <c r="F50" t="n">
-        <v>9.281000000000001</v>
+        <v>9.294</v>
       </c>
       <c r="G50" t="n">
-        <v>27.156</v>
+        <v>27.412</v>
       </c>
       <c r="H50" t="n">
-        <v>17.594</v>
+        <v>17.353</v>
       </c>
       <c r="I50" t="n">
-        <v>22.781</v>
+        <v>22.471</v>
       </c>
       <c r="J50" t="n">
-        <v>17.781</v>
+        <v>17.647</v>
       </c>
       <c r="K50" t="n">
-        <v>26</v>
+        <v>25.706</v>
       </c>
       <c r="L50" t="n">
-        <v>10.25</v>
+        <v>10.559</v>
       </c>
       <c r="M50" t="n">
-        <v>7.469</v>
+        <v>7.441</v>
       </c>
       <c r="N50" t="n">
-        <v>5.688</v>
+        <v>5.441</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>13.844</v>
+        <v>13.824</v>
       </c>
       <c r="Q50" t="n">
-        <v>12.688</v>
+        <v>12.676</v>
       </c>
       <c r="R50" t="n">
-        <v>23.344</v>
+        <v>23.529</v>
       </c>
       <c r="S50" t="n">
-        <v>22.344</v>
+        <v>22.206</v>
       </c>
       <c r="T50" t="n">
-        <v>3154</v>
+        <v>3307</v>
       </c>
       <c r="U50" t="n">
-        <v>11.406</v>
+        <v>11.147</v>
       </c>
       <c r="V50" t="n">
-        <v>10.531</v>
+        <v>10.647</v>
       </c>
       <c r="W50" t="n">
-        <v>6</v>
+        <v>5.882</v>
       </c>
       <c r="X50" t="n">
-        <v>3.719</v>
+        <v>3.647</v>
       </c>
       <c r="Y50" t="n">
-        <v>30.344</v>
+        <v>30.147</v>
       </c>
       <c r="Z50" t="n">
-        <v>41.781</v>
+        <v>41.471</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.726</v>
+        <v>0.727</v>
       </c>
       <c r="AB50" t="n">
-        <v>4.625</v>
+        <v>4.529</v>
       </c>
       <c r="AC50" t="n">
-        <v>10.438</v>
+        <v>10.294</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.443</v>
+        <v>0.44</v>
       </c>
       <c r="AE50" t="n">
-        <v>3.062</v>
+        <v>3.059</v>
       </c>
       <c r="AF50" t="n">
-        <v>8.031000000000001</v>
+        <v>8.234999999999999</v>
       </c>
       <c r="AG50" t="n">
-        <v>0.381</v>
+        <v>0.371</v>
       </c>
       <c r="AH50" t="n">
-        <v>2</v>
+        <v>1.941</v>
       </c>
       <c r="AI50" t="n">
-        <v>5.656</v>
+        <v>5.588</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0.354</v>
+        <v>0.347</v>
       </c>
       <c r="AK50" t="n">
-        <v>7.281</v>
+        <v>7.353</v>
       </c>
       <c r="AL50" t="n">
-        <v>21.5</v>
+        <v>21.824</v>
       </c>
       <c r="AM50" t="n">
-        <v>0.339</v>
+        <v>0.337</v>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>202:20</t>
+          <t>202:12</t>
         </is>
       </c>
       <c r="AO50" t="n">
-        <v>88.492</v>
+        <v>88.652</v>
       </c>
       <c r="AP50" t="n">
-        <v>0.532</v>
+        <v>0.529</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0.578</v>
+        <v>0.575</v>
       </c>
       <c r="AR50" t="n">
-        <v>0.975</v>
+        <v>0.97</v>
       </c>
       <c r="AS50" t="n">
         <v>0.156</v>
       </c>
       <c r="AT50" t="n">
-        <v>0.272</v>
+        <v>0.267</v>
       </c>
       <c r="AU50" t="n">
-        <v>1.284</v>
+        <v>1.277</v>
       </c>
       <c r="AV50" t="n">
-        <v>0.202</v>
+        <v>0.203</v>
       </c>
       <c r="AW50" t="n">
-        <v>0.058</v>
+        <v>0.06</v>
       </c>
       <c r="AX50" t="n">
-        <v>0.146</v>
+        <v>0.143</v>
       </c>
       <c r="AY50" t="n">
         <v>0</v>
